--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:21 AM PT</t>
+          <t>2026-07-12 08:54:21 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:23 AM PT</t>
+          <t>2026-07-12 08:54:23 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 08:52:22 AM PT</t>
+          <t>2026-07-12 08:54:22 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:21 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:23 AM PT</t>
+          <t>2026-07-12 08:56:22 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 08:54:22 AM PT</t>
+          <t>2026-07-12 08:56:21 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:22 AM PT</t>
+          <t>2026-07-12 08:58:22 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 08:56:21 AM PT</t>
+          <t>2026-07-12 08:58:21 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:22 AM PT</t>
+          <t>2026-07-12 09:00:22 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 08:58:21 AM PT</t>
+          <t>2026-07-12 09:00:21 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:22 AM PT</t>
+          <t>2026-07-12 09:02:22 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:00:21 AM PT</t>
+          <t>2026-07-12 09:02:21 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -82,6 +87,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -663,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -676,7 +682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -688,7 +694,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -713,20 +719,20 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>656811</v>
+        <v>680779</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -741,20 +747,20 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -769,13 +775,13 @@
         <v>0</v>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -786,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -799,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -811,7 +817,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -836,20 +842,20 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Esmerlyn Valdez</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>699013</v>
+        <v>656811</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -864,7 +870,7 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
@@ -877,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -892,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -909,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -922,7 +928,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,7 +940,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -959,20 +965,20 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Esmerlyn Valdez</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>542303</v>
+        <v>699013</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -985,11 +991,11 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
@@ -997,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1015,13 +1021,13 @@
         <v>0</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1032,74 +1038,83 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>824574</v>
+        <v>823358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Marcell Ozuna</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>542303</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Jacob Wilson</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>805779</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1111,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1129,13 +1144,13 @@
         <v>0</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1146,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1187,20 +1202,20 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>811965</v>
+        <v>805779</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1260,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1301,20 +1316,20 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>669127</v>
+        <v>811965</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1374,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1415,20 +1430,20 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>641680</v>
+        <v>669127</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R8" t="n">
@@ -1488,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1529,20 +1544,20 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Colby Thomas</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>687515</v>
+        <v>641680</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1602,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1643,20 +1658,20 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Joey Meneses</t>
+          <t>Colby Thomas</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>608841</v>
+        <v>687515</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1716,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1757,20 +1772,20 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Joey Meneses</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>671732</v>
+        <v>608841</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1830,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1871,20 +1886,20 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>703607</v>
+        <v>671732</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R12" t="n">
@@ -1944,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1985,20 +2000,20 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>675961</v>
+        <v>703607</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -2058,15 +2073,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>823029</v>
+        <v>824574</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2089,30 +2104,30 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>686948</v>
+        <v>675961</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -2172,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2213,20 +2228,20 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>645277</v>
+        <v>686948</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2286,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2327,20 +2342,20 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>621566</v>
+        <v>645277</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R16" t="n">
@@ -2400,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2441,20 +2456,20 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>671739</v>
+        <v>621566</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2514,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2555,20 +2570,20 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>643289</v>
+        <v>671739</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2628,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2669,20 +2684,20 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>642086</v>
+        <v>643289</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2742,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2783,20 +2798,20 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>663586</v>
+        <v>642086</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2856,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2897,20 +2912,20 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>805347</v>
+        <v>663586</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -2970,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3011,20 +3026,20 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>676551</v>
+        <v>805347</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R22" t="n">
@@ -3084,15 +3099,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>824814</v>
+        <v>823029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3110,35 +3125,35 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>683002</v>
+        <v>676551</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -3198,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3239,20 +3254,20 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>621493</v>
+        <v>683002</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -3312,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3353,20 +3368,20 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>687637</v>
+        <v>621493</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -3426,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3467,20 +3482,20 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>624413</v>
+        <v>687637</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -3540,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3581,20 +3596,20 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>694212</v>
+        <v>624413</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -3654,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3695,20 +3710,20 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Blaze Alexander</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>677942</v>
+        <v>694212</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3768,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3809,20 +3824,20 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Blaze Alexander</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>681297</v>
+        <v>677942</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -3882,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3923,20 +3938,20 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>665750</v>
+        <v>681297</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -3996,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4037,20 +4052,20 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>702616</v>
+        <v>665750</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -4110,15 +4125,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>823602</v>
+        <v>824814</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4136,26 +4151,26 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>678011</v>
+        <v>702616</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -4164,7 +4179,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -4224,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4265,20 +4280,20 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>678882</v>
+        <v>678011</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -4338,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4379,20 +4394,20 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>677800</v>
+        <v>678882</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -4452,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4493,20 +4508,20 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Romy Gonzalez</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>663853</v>
+        <v>677800</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -4566,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4607,20 +4622,20 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Romy Gonzalez</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>702332</v>
+        <v>663853</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -4680,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4721,20 +4736,20 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>655316</v>
+        <v>702332</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -4794,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4835,20 +4850,20 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>680776</v>
+        <v>655316</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -4908,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4949,20 +4964,20 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>681987</v>
+        <v>680776</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -5022,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5063,20 +5078,20 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>657136</v>
+        <v>681987</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -5136,11 +5151,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>824491</v>
+        <v>823602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,30 +5182,30 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>691718</v>
+        <v>657136</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -5250,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5291,20 +5306,20 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>673548</v>
+        <v>691718</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -5364,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5405,20 +5420,20 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>608324</v>
+        <v>673548</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -5478,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5519,20 +5534,20 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>608348</v>
+        <v>608324</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -5592,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5633,20 +5648,20 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>683737</v>
+        <v>608348</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -5706,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5747,20 +5762,20 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>663538</v>
+        <v>683737</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -5820,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5861,20 +5876,20 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>664023</v>
+        <v>663538</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -5934,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5975,20 +5990,20 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>621020</v>
+        <v>664023</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -6048,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6089,20 +6104,20 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Kevin Alcántara</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>682634</v>
+        <v>621020</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -6162,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6188,35 +6203,35 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Kevin Alcántara</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>682829</v>
+        <v>682634</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -6276,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6317,20 +6332,20 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>701398</v>
+        <v>682829</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -6390,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6431,20 +6446,20 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>668715</v>
+        <v>701398</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -6504,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6545,20 +6560,20 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>668709</v>
+        <v>668715</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -6618,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6659,20 +6674,20 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>553993</v>
+        <v>668709</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R54" t="n">
@@ -6732,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6773,20 +6788,20 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>663886</v>
+        <v>553993</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -6846,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6887,20 +6902,20 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>682622</v>
+        <v>663886</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R56" t="n">
@@ -6960,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7001,20 +7016,20 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Edwin Arroyo</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>695490</v>
+        <v>682622</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -7074,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7115,20 +7130,20 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Edwin Arroyo</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>663647</v>
+        <v>695490</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R58" t="n">
@@ -7188,11 +7203,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>823842</v>
+        <v>824491</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7214,35 +7229,35 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>683953</v>
+        <v>663647</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -7302,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7343,20 +7358,20 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>677587</v>
+        <v>683953</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R60" t="n">
@@ -7416,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7457,20 +7472,20 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>800050</v>
+        <v>677587</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R61" t="n">
@@ -7530,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7571,20 +7586,20 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>700932</v>
+        <v>800050</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -7644,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7685,20 +7700,20 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -7758,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7799,20 +7814,20 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>672356</v>
+        <v>696135</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -7872,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7913,20 +7928,20 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>690984</v>
+        <v>672356</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -7986,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8027,20 +8042,20 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>672275</v>
+        <v>690984</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R66" t="n">
@@ -8100,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8141,20 +8156,20 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>680757</v>
+        <v>672275</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8214,15 +8229,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>824574</v>
+        <v>823842</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8240,26 +8255,26 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>803011</v>
+        <v>680757</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -8268,7 +8283,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R68" t="n">
@@ -8328,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8369,20 +8384,20 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>808959</v>
+        <v>803011</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -8442,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8483,20 +8498,20 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>678246</v>
+        <v>808959</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -8556,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8597,20 +8612,20 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>695657</v>
+        <v>678246</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8670,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8711,20 +8726,20 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>643217</v>
+        <v>695657</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -8784,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8825,20 +8840,20 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>691019</v>
+        <v>643217</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -8898,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8939,20 +8954,20 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>695731</v>
+        <v>691019</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -9012,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9053,20 +9068,20 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>671976</v>
+        <v>695731</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -9126,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9167,20 +9182,20 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>805367</v>
+        <v>671976</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R76" t="n">
@@ -9240,15 +9255,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>824250</v>
+        <v>824574</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9271,30 +9286,30 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>805808</v>
+        <v>805367</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9354,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9395,20 +9410,20 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>693307</v>
+        <v>805808</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R78" t="n">
@@ -9468,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9509,20 +9524,20 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>690993</v>
+        <v>693307</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -9582,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9623,20 +9638,20 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>682985</v>
+        <v>690993</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R80" t="n">
@@ -9696,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9737,20 +9752,20 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>679529</v>
+        <v>682985</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -9810,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9851,20 +9866,20 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Kerry Carpenter</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>681481</v>
+        <v>679529</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R82" t="n">
@@ -9924,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -9965,20 +9980,20 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Kerry Carpenter</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>656716</v>
+        <v>681481</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -10038,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10079,20 +10094,20 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>663837</v>
+        <v>656716</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R84" t="n">
@@ -10152,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10193,20 +10208,20 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>681546</v>
+        <v>663837</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -10266,15 +10281,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>822876</v>
+        <v>824250</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10292,35 +10307,35 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>665161</v>
+        <v>681546</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R86" t="n">
@@ -10380,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10421,20 +10436,20 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>670541</v>
+        <v>665161</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -10494,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10535,20 +10550,20 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>670623</v>
+        <v>670541</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R88" t="n">
@@ -10608,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10649,20 +10664,20 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>572233</v>
+        <v>670623</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R89" t="n">
@@ -10722,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10763,20 +10778,20 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>514888</v>
+        <v>572233</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R90" t="n">
@@ -10836,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10877,20 +10892,20 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>701358</v>
+        <v>514888</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -10950,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -10991,20 +11006,20 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>664774</v>
+        <v>701358</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R92" t="n">
@@ -11064,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11105,20 +11120,20 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Brice Matthews</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>694728</v>
+        <v>664774</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -11178,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11219,20 +11234,20 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Brice Matthews</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>543877</v>
+        <v>694728</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R94" t="n">
@@ -11292,15 +11307,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>824814</v>
+        <v>822876</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11323,21 +11338,21 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>695600</v>
+        <v>543877</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -11346,7 +11361,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -11406,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11447,20 +11462,20 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>677951</v>
+        <v>695600</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R96" t="n">
@@ -11520,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11561,20 +11576,20 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>695506</v>
+        <v>677951</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R97" t="n">
@@ -11634,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11675,20 +11690,20 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>657041</v>
+        <v>695506</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R98" t="n">
@@ -11748,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11789,20 +11804,20 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>686469</v>
+        <v>657041</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -11862,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11903,20 +11918,20 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>521692</v>
+        <v>686469</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R100" t="n">
@@ -11976,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12017,20 +12032,20 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>686681</v>
+        <v>521692</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R101" t="n">
@@ -12090,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12131,20 +12146,20 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Josh Rojas</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>668942</v>
+        <v>686681</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R102" t="n">
@@ -12204,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12245,20 +12260,20 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Rojas</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>686555</v>
+        <v>668942</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -12318,15 +12333,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>823681</v>
+        <v>824814</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12349,30 +12364,30 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>687263</v>
+        <v>686555</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -12432,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12473,20 +12488,20 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>545361</v>
+        <v>687263</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -12546,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12587,20 +12602,20 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>694384</v>
+        <v>545361</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R106" t="n">
@@ -12660,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12701,20 +12716,20 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>624585</v>
+        <v>694384</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -12774,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12815,20 +12830,20 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>666176</v>
+        <v>624585</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R108" t="n">
@@ -12888,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12929,20 +12944,20 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>666139</v>
+        <v>666176</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -13002,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13043,20 +13058,20 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>672724</v>
+        <v>666139</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R110" t="n">
@@ -13116,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13157,20 +13172,20 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>694203</v>
+        <v>672724</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -13230,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13271,20 +13286,20 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>681351</v>
+        <v>694203</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R112" t="n">
@@ -13344,15 +13359,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>823842</v>
+        <v>823681</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -13370,35 +13385,35 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>672640</v>
+        <v>681351</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -13458,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13499,20 +13514,20 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>681715</v>
+        <v>672640</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R114" t="n">
@@ -13572,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13613,20 +13628,20 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>689414</v>
+        <v>681715</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -13686,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13727,20 +13742,20 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>669364</v>
+        <v>689414</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R116" t="n">
@@ -13800,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13841,20 +13856,20 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>691594</v>
+        <v>669364</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -13914,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -13955,20 +13970,20 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Leo Jiménez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>677870</v>
+        <v>691594</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -14028,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14069,20 +14084,20 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Leo Jiménez</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>665923</v>
+        <v>677870</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -14142,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14183,20 +14198,20 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Rece Hinds</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>677956</v>
+        <v>665923</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R120" t="n">
@@ -14256,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14297,20 +14312,20 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>640459</v>
+        <v>677956</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -14370,77 +14385,68 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>823358</v>
+        <v>823842</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>1</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>592885</v>
+        <v>640459</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
         <v>0</v>
@@ -14493,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14506,7 +14512,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -14518,7 +14524,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -14543,20 +14549,20 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>694192</v>
+        <v>592885</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -14596,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE123" s="4" t="n">
         <v>0</v>
@@ -14616,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14629,7 +14635,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14641,7 +14647,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -14666,20 +14672,20 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>668930</v>
+        <v>694192</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R124" t="n">
@@ -14719,7 +14725,7 @@
         <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE124" s="4" t="n">
         <v>0</v>
@@ -14739,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14752,7 +14758,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14764,7 +14770,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -14789,20 +14795,20 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>641343</v>
+        <v>668930</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -14862,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14875,7 +14881,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14887,7 +14893,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -14912,20 +14918,20 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>596142</v>
+        <v>641343</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R126" t="n">
@@ -14985,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -14998,7 +15004,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15010,7 +15016,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -15035,20 +15041,20 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>669003</v>
+        <v>596142</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -15108,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15121,7 +15127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15133,52 +15139,52 @@
         </is>
       </c>
       <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Garrett Mitchell</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>669003</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
         <v>1</v>
       </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>Sal Frelick</t>
-        </is>
-      </c>
-      <c r="O128" t="n">
-        <v>686217</v>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
         <v>0</v>
@@ -15231,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15244,7 +15250,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15256,7 +15262,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -15281,20 +15287,20 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>687401</v>
+        <v>686217</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R129" t="n">
@@ -15354,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15367,7 +15373,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15379,7 +15385,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -15404,20 +15410,20 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Braden Shewmake</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>669699</v>
+        <v>687401</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R130" t="n">
@@ -15477,61 +15483,70 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>823681</v>
+        <v>823358</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Top</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Braden Shewmake</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>663616</v>
+        <v>669699</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R131" t="n">
@@ -15591,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15632,20 +15647,20 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>680777</v>
+        <v>663616</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R132" t="n">
@@ -15705,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15746,20 +15761,20 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>605137</v>
+        <v>680777</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R133" t="n">
@@ -15819,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15860,20 +15875,20 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>665019</v>
+        <v>605137</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R134" t="n">
@@ -15933,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -15974,20 +15989,20 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>668904</v>
+        <v>665019</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -16047,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16088,20 +16103,20 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>686797</v>
+        <v>668904</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R136" t="n">
@@ -16161,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16202,20 +16217,20 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Alan Roden</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>702176</v>
+        <v>686797</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R137" t="n">
@@ -16275,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16316,20 +16331,20 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Alan Roden</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>807712</v>
+        <v>702176</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R138" t="n">
@@ -16389,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16430,20 +16445,20 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>668952</v>
+        <v>807712</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -16503,15 +16518,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>823602</v>
+        <v>823681</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -16534,30 +16549,30 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>A.J. Ewing</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>805999</v>
+        <v>668952</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R140" t="n">
@@ -16617,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16658,20 +16673,20 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>A.J. Ewing</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>665742</v>
+        <v>805999</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -16731,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16772,20 +16787,20 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>596019</v>
+        <v>665742</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R142" t="n">
@@ -16845,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16886,20 +16901,20 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Eric Wagaman</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>676572</v>
+        <v>596019</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -16959,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17000,20 +17015,20 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Eric Wagaman</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>701807</v>
+        <v>676572</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R144" t="n">
@@ -17073,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17114,20 +17129,20 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Tyrone Taylor</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>621438</v>
+        <v>701807</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R145" t="n">
@@ -17187,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17228,20 +17243,20 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Luis Torrens</t>
+          <t>Tyrone Taylor</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>620443</v>
+        <v>621438</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R146" t="n">
@@ -17301,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17342,20 +17357,20 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Luis Torrens</t>
         </is>
       </c>
       <c r="O147" t="n">
-        <v>683146</v>
+        <v>620443</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -17415,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17456,20 +17471,20 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Zack Short</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>670097</v>
+        <v>683146</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R148" t="n">
@@ -17529,15 +17544,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>822708</v>
+        <v>823602</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -17555,35 +17570,35 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Zack Short</t>
         </is>
       </c>
       <c r="O149" t="n">
-        <v>663757</v>
+        <v>670097</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R149" t="n">
@@ -17643,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17684,20 +17699,20 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>700250</v>
+        <v>663757</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R150" t="n">
@@ -17757,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17798,20 +17813,20 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Jasson Domínguez</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="O151" t="n">
-        <v>691176</v>
+        <v>700250</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R151" t="n">
@@ -17871,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17912,20 +17927,20 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Jasson Domínguez</t>
         </is>
       </c>
       <c r="O152" t="n">
-        <v>641355</v>
+        <v>691176</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R152" t="n">
@@ -17985,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18026,20 +18041,20 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="O153" t="n">
-        <v>665862</v>
+        <v>641355</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R153" t="n">
@@ -18099,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18140,20 +18155,20 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>José Caballero</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="O154" t="n">
-        <v>676609</v>
+        <v>665862</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R154" t="n">
@@ -18213,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18254,20 +18269,20 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="O155" t="n">
-        <v>641857</v>
+        <v>676609</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R155" t="n">
@@ -18327,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18368,20 +18383,20 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="O156" t="n">
-        <v>669224</v>
+        <v>641857</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R156" t="n">
@@ -18441,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18482,20 +18497,20 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Max Schuemann</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="O157" t="n">
-        <v>680474</v>
+        <v>669224</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R157" t="n">
@@ -18555,15 +18570,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>824250</v>
+        <v>822708</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -18586,30 +18601,30 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Max Schuemann</t>
         </is>
       </c>
       <c r="O158" t="n">
-        <v>607208</v>
+        <v>680474</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R158" t="n">
@@ -18669,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18710,20 +18725,20 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="O159" t="n">
-        <v>656941</v>
+        <v>607208</v>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R159" t="n">
@@ -18783,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18824,20 +18839,20 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="O160" t="n">
-        <v>547180</v>
+        <v>656941</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R160" t="n">
@@ -18897,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -18938,20 +18953,20 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="O161" t="n">
-        <v>664761</v>
+        <v>547180</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R161" t="n">
@@ -19011,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19052,20 +19067,20 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="O162" t="n">
-        <v>624641</v>
+        <v>664761</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R162" t="n">
@@ -19125,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19166,20 +19181,20 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="O163" t="n">
-        <v>669016</v>
+        <v>624641</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R163" t="n">
@@ -19239,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19280,20 +19295,20 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="O164" t="n">
-        <v>656537</v>
+        <v>669016</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R164" t="n">
@@ -19353,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19394,20 +19409,20 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="O165" t="n">
-        <v>592663</v>
+        <v>656537</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R165" t="n">
@@ -19467,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19508,20 +19523,20 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="O166" t="n">
-        <v>681082</v>
+        <v>592663</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R166" t="n">
@@ -19581,77 +19596,68 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>823358</v>
+        <v>824250</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H167" t="n">
-        <v>1</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="O167" t="n">
-        <v>663968</v>
+        <v>681082</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T167" t="n">
         <v>0</v>
@@ -19690,10 +19696,10 @@
         <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -19704,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19717,7 +19723,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -19729,7 +19735,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -19754,20 +19760,20 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="O168" t="n">
-        <v>664040</v>
+        <v>663968</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R168" t="n">
@@ -19807,16 +19813,16 @@
         <v>0</v>
       </c>
       <c r="AD168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE168" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
@@ -19827,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19840,7 +19846,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19852,7 +19858,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -19877,20 +19883,20 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="O169" t="n">
-        <v>668804</v>
+        <v>664040</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R169" t="n">
@@ -19936,10 +19942,10 @@
         <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -19950,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19963,7 +19969,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19975,7 +19981,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -20000,20 +20006,20 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="O170" t="n">
-        <v>693304</v>
+        <v>668804</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R170" t="n">
@@ -20053,16 +20059,16 @@
         <v>0</v>
       </c>
       <c r="AD170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE170" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AF170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
@@ -20073,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20086,7 +20092,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20098,52 +20104,52 @@
         </is>
       </c>
       <c r="H171" t="n">
+        <v>2</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Nick Gonzales</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>693304</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R171" t="n">
         <v>1</v>
       </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>Jared Triolo</t>
-        </is>
-      </c>
-      <c r="O171" t="n">
-        <v>669707</v>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
       <c r="S171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171" t="n">
         <v>0</v>
@@ -20182,10 +20188,10 @@
         <v>0</v>
       </c>
       <c r="AF171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
@@ -20196,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20209,7 +20215,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 2 | 1 out</t>
+          <t>Bottom 2 | 2 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20221,52 +20227,52 @@
         </is>
       </c>
       <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Jared Triolo</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>669707</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R172" t="n">
         <v>1</v>
       </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>Henry Davis</t>
-        </is>
-      </c>
-      <c r="O172" t="n">
-        <v>680779</v>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T172" t="n">
         <v>0</v>
@@ -20305,10 +20311,10 @@
         <v>0</v>
       </c>
       <c r="AF172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
@@ -20319,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20433,7 +20439,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20547,7 +20553,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20661,7 +20667,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20775,7 +20781,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20889,7 +20895,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21003,7 +21009,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21117,7 +21123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21231,7 +21237,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21345,7 +21351,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21451,7 +21457,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21557,7 +21563,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21663,7 +21669,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21769,7 +21775,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21875,7 +21881,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21981,7 +21987,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22087,7 +22093,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22193,7 +22199,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22299,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22413,7 +22419,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22527,7 +22533,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22641,7 +22647,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22755,7 +22761,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22869,7 +22875,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22983,7 +22989,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23097,7 +23103,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23211,7 +23217,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23325,7 +23331,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23439,7 +23445,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23553,7 +23559,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23667,7 +23673,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23781,7 +23787,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23895,7 +23901,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24009,7 +24015,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24123,7 +24129,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24237,7 +24243,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24351,7 +24357,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24465,7 +24471,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24579,7 +24585,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24693,7 +24699,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24807,7 +24813,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24921,7 +24927,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25035,7 +25041,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25149,7 +25155,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25263,7 +25269,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:34 AM PT</t>
+          <t>2026-07-12 09:43:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25377,7 +25383,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25491,7 +25497,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25605,7 +25611,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25719,7 +25725,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25833,7 +25839,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25947,7 +25953,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26061,7 +26067,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26175,7 +26181,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26289,7 +26295,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:41:33 AM PT</t>
+          <t>2026-07-12 09:43:33 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26427,12 +26433,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Stat Type</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -697,10 +697,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,10 +820,10 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -943,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1066,10 +1066,10 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14527,10 +14527,10 @@
         <v>2</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14650,10 +14650,10 @@
         <v>2</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14773,10 +14773,10 @@
         <v>2</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14896,10 +14896,10 @@
         <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15019,10 +15019,10 @@
         <v>2</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15142,10 +15142,10 @@
         <v>2</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15265,10 +15265,10 @@
         <v>2</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15388,10 +15388,10 @@
         <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15511,10 +15511,10 @@
         <v>2</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19738,10 +19738,10 @@
         <v>2</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19861,10 +19861,10 @@
         <v>2</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19984,10 +19984,10 @@
         <v>2</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20107,10 +20107,10 @@
         <v>2</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20230,10 +20230,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21775,7 +21775,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21987,7 +21987,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:34 AM PT</t>
+          <t>2026-07-12 09:45:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:43:33 AM PT</t>
+          <t>2026-07-12 09:45:33 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -463,7 +463,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,25 +682,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -805,25 +805,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -928,25 +928,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1051,25 +1051,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14512,25 +14512,25 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14635,25 +14635,25 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14758,25 +14758,25 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14881,25 +14881,25 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15004,25 +15004,25 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15127,25 +15127,25 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15250,25 +15250,25 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15373,25 +15373,25 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15496,25 +15496,25 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19723,25 +19723,25 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -19777,10 +19777,10 @@
         </is>
       </c>
       <c r="R168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T168" t="n">
         <v>0</v>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19846,25 +19846,25 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19969,25 +19969,25 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20092,25 +20092,25 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20215,25 +20215,25 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 2 | 2 out</t>
+          <t>Top 3 | 0 out</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21775,7 +21775,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21987,7 +21987,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:34 AM PT</t>
+          <t>2026-07-12 09:47:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:45:33 AM PT</t>
+          <t>2026-07-12 09:47:33 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,10 +820,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1066,10 +1066,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14527,10 +14527,10 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14650,10 +14650,10 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14773,10 +14773,10 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14896,10 +14896,10 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15019,10 +15019,10 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15142,10 +15142,10 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15265,10 +15265,10 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15388,10 +15388,10 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15511,10 +15511,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19738,10 +19738,10 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19861,10 +19861,10 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19984,10 +19984,10 @@
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20230,10 +20230,10 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21775,7 +21775,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21987,7 +21987,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:34 AM PT</t>
+          <t>2026-07-12 09:49:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:47:33 AM PT</t>
+          <t>2026-07-12 09:49:33 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Fantasy Scores'!$A$1:$AG$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG226"/>
+  <dimension ref="A1:AG235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>2</v>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
         <v>2</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
         <v>2</v>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>2</v>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15016,10 +15016,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>2</v>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15139,10 +15139,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
         <v>2</v>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>2</v>
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
         <v>0</v>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15385,10 +15385,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>2</v>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>2</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
         <v>2</v>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19858,10 +19858,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
         <v>2</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>2</v>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20104,10 +20104,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>2</v>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 3 | 0 out</t>
+          <t>Top 3 | 1 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20227,10 +20227,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>2</v>
@@ -20325,15 +20325,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -20341,40 +20341,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F173" t="n">
-        <v>1</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="O173" t="n">
-        <v>641487</v>
+        <v>665487</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -20439,15 +20431,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -20455,40 +20447,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F174" t="n">
-        <v>1</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="O174" t="n">
-        <v>668227</v>
+        <v>701538</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -20553,15 +20537,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -20569,40 +20553,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="O175" t="n">
-        <v>663728</v>
+        <v>593428</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -20667,15 +20643,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -20683,40 +20659,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="O176" t="n">
-        <v>647304</v>
+        <v>592518</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -20781,15 +20749,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -20797,40 +20765,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>Mitch Garver</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="O177" t="n">
-        <v>641598</v>
+        <v>657757</v>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -20895,15 +20855,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -20911,40 +20871,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="O178" t="n">
-        <v>702284</v>
+        <v>664034</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -21009,15 +20961,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -21025,40 +20977,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="O179" t="n">
-        <v>645302</v>
+        <v>630105</v>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -21123,15 +21067,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -21139,40 +21083,32 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F180" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="O180" t="n">
-        <v>642215</v>
+        <v>669134</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -21237,15 +21173,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>822951</v>
+        <v>823274</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -21253,36 +21189,28 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F181" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>Buddy Kennedy</t>
+          <t>Sung-Mun Song</t>
         </is>
       </c>
       <c r="O181" t="n">
-        <v>671083</v>
+        <v>823550</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -21351,15 +21279,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -21367,32 +21295,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="O182" t="n">
-        <v>671218</v>
+        <v>641487</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -21457,15 +21393,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -21473,32 +21409,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="O183" t="n">
-        <v>650333</v>
+        <v>668227</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -21563,15 +21507,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -21579,32 +21523,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="O184" t="n">
-        <v>669477</v>
+        <v>663728</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -21669,15 +21621,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -21685,28 +21637,36 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="O185" t="n">
-        <v>646240</v>
+        <v>647304</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
@@ -21775,15 +21735,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -21791,32 +21751,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Mitch Garver</t>
         </is>
       </c>
       <c r="O186" t="n">
-        <v>808982</v>
+        <v>641598</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -21881,15 +21849,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -21897,32 +21865,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="O187" t="n">
-        <v>805811</v>
+        <v>702284</v>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
@@ -21987,15 +21963,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -22003,32 +21979,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="O188" t="n">
-        <v>642715</v>
+        <v>645302</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -22093,15 +22077,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -22109,32 +22093,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="O189" t="n">
-        <v>687551</v>
+        <v>642215</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -22199,15 +22191,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>823199</v>
+        <v>822951</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -22215,32 +22207,40 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Buddy Kennedy</t>
         </is>
       </c>
       <c r="O190" t="n">
-        <v>701852</v>
+        <v>671083</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -22305,15 +22305,15 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -22321,14 +22321,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F191" t="n">
-        <v>1</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K191" t="inlineStr">
         <is>
           <t>Home</t>
@@ -22336,25 +22328,25 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="O191" t="n">
-        <v>802139</v>
+        <v>671218</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -22419,15 +22411,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -22435,14 +22427,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F192" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K192" t="inlineStr">
         <is>
           <t>Home</t>
@@ -22450,25 +22434,25 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>Iván Herrera</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="O192" t="n">
-        <v>671056</v>
+        <v>650333</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -22533,15 +22517,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -22549,14 +22533,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F193" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>Home</t>
@@ -22564,25 +22540,25 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="O193" t="n">
-        <v>691023</v>
+        <v>669477</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -22647,15 +22623,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -22663,14 +22639,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F194" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>Home</t>
@@ -22678,21 +22646,21 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="O194" t="n">
-        <v>676475</v>
+        <v>646240</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -22761,15 +22729,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -22777,14 +22745,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F195" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K195" t="inlineStr">
         <is>
           <t>Home</t>
@@ -22792,25 +22752,25 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="O195" t="n">
-        <v>663457</v>
+        <v>808982</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -22875,15 +22835,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -22891,14 +22851,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K196" t="inlineStr">
         <is>
           <t>Home</t>
@@ -22906,25 +22858,25 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="O196" t="n">
-        <v>691026</v>
+        <v>805811</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -22989,15 +22941,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -23005,14 +22957,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F197" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K197" t="inlineStr">
         <is>
           <t>Home</t>
@@ -23020,25 +22964,25 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="O197" t="n">
-        <v>701675</v>
+        <v>642715</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -23103,15 +23047,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -23119,14 +23063,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K198" t="inlineStr">
         <is>
           <t>Home</t>
@@ -23134,25 +23070,25 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>José Fermín</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="O198" t="n">
-        <v>665877</v>
+        <v>687551</v>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -23217,15 +23153,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>823029</v>
+        <v>823199</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -23233,14 +23169,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F199" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K199" t="inlineStr">
         <is>
           <t>Home</t>
@@ -23248,21 +23176,21 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Jimmy Crooks</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="O199" t="n">
-        <v>699625</v>
+        <v>701852</v>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -23331,15 +23259,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -23362,25 +23290,25 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="O200" t="n">
-        <v>650490</v>
+        <v>802139</v>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -23445,15 +23373,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -23476,25 +23404,25 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Iván Herrera</t>
         </is>
       </c>
       <c r="O201" t="n">
-        <v>666018</v>
+        <v>671056</v>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -23559,15 +23487,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -23590,25 +23518,25 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="O202" t="n">
-        <v>691406</v>
+        <v>691023</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
@@ -23673,15 +23601,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -23704,25 +23632,25 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="O203" t="n">
-        <v>656775</v>
+        <v>676475</v>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -23787,15 +23715,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -23818,21 +23746,21 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="O204" t="n">
-        <v>802415</v>
+        <v>663457</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -23901,15 +23829,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -23932,25 +23860,25 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="O205" t="n">
-        <v>683748</v>
+        <v>691026</v>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -24015,15 +23943,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -24046,25 +23974,25 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="O206" t="n">
-        <v>670764</v>
+        <v>701675</v>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -24129,15 +24057,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -24160,25 +24088,25 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>José Fermín</t>
         </is>
       </c>
       <c r="O207" t="n">
-        <v>680700</v>
+        <v>665877</v>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -24243,15 +24171,15 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>822951</v>
+        <v>823029</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -24274,21 +24202,21 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Jimmy Crooks</t>
         </is>
       </c>
       <c r="O208" t="n">
-        <v>676439</v>
+        <v>699625</v>
       </c>
       <c r="P208" t="inlineStr">
         <is>
@@ -24357,15 +24285,15 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -24388,21 +24316,21 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="O209" t="n">
-        <v>592626</v>
+        <v>650490</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
@@ -24471,15 +24399,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -24502,25 +24430,25 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="O210" t="n">
-        <v>694671</v>
+        <v>666018</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -24585,15 +24513,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -24616,21 +24544,21 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="O211" t="n">
-        <v>673962</v>
+        <v>691406</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -24699,15 +24627,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -24730,25 +24658,25 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="O212" t="n">
-        <v>607043</v>
+        <v>656775</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -24813,15 +24741,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -24844,25 +24772,25 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="O213" t="n">
-        <v>669394</v>
+        <v>802415</v>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -24927,15 +24855,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -24958,25 +24886,25 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="O214" t="n">
-        <v>677649</v>
+        <v>683748</v>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -25041,15 +24969,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -25072,25 +25000,25 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="O215" t="n">
-        <v>694497</v>
+        <v>670764</v>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -25155,15 +25083,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -25186,21 +25114,21 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="O216" t="n">
-        <v>670032</v>
+        <v>680700</v>
       </c>
       <c r="P216" t="inlineStr">
         <is>
@@ -25269,15 +25197,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:34 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>822876</v>
+        <v>822951</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -25300,21 +25228,21 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Kyle Higashioka</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="O217" t="n">
-        <v>543309</v>
+        <v>676439</v>
       </c>
       <c r="P217" t="inlineStr">
         <is>
@@ -25383,15 +25311,15 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -25414,25 +25342,25 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="O218" t="n">
-        <v>695578</v>
+        <v>592626</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -25497,15 +25425,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -25528,25 +25456,25 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="O219" t="n">
-        <v>671277</v>
+        <v>694671</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -25611,15 +25539,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -25642,25 +25570,25 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>Abimelec Ortiz</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="O220" t="n">
-        <v>694673</v>
+        <v>673962</v>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -25725,15 +25653,15 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -25756,25 +25684,25 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="O221" t="n">
-        <v>682928</v>
+        <v>607043</v>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -25839,15 +25767,15 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -25870,25 +25798,25 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="O222" t="n">
-        <v>686611</v>
+        <v>669394</v>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -25953,15 +25881,15 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -25984,25 +25912,25 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="O223" t="n">
-        <v>695734</v>
+        <v>677649</v>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -26067,15 +25995,15 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -26098,25 +26026,25 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="O224" t="n">
-        <v>677588</v>
+        <v>694497</v>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -26181,15 +26109,15 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -26212,25 +26140,25 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="O225" t="n">
-        <v>678391</v>
+        <v>670032</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -26295,15 +26223,15 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:49:33 AM PT</t>
+          <t>2026-07-12 09:51:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>822708</v>
+        <v>822876</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -26326,84 +26254,1110 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Kyle Higashioka</t>
+        </is>
+      </c>
+      <c r="O226" t="n">
+        <v>543309</v>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0</v>
+      </c>
+      <c r="V226" t="n">
+        <v>0</v>
+      </c>
+      <c r="W226" t="n">
+        <v>0</v>
+      </c>
+      <c r="X226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="O227" t="n">
+        <v>695578</v>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0</v>
+      </c>
+      <c r="V227" t="n">
+        <v>0</v>
+      </c>
+      <c r="W227" t="n">
+        <v>0</v>
+      </c>
+      <c r="X227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE227" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Luis García Jr.</t>
+        </is>
+      </c>
+      <c r="O228" t="n">
+        <v>671277</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>0</v>
+      </c>
+      <c r="V228" t="n">
+        <v>0</v>
+      </c>
+      <c r="W228" t="n">
+        <v>0</v>
+      </c>
+      <c r="X228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Abimelec Ortiz</t>
+        </is>
+      </c>
+      <c r="O229" t="n">
+        <v>694673</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>0</v>
+      </c>
+      <c r="V229" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" t="n">
+        <v>0</v>
+      </c>
+      <c r="X229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>CJ Abrams</t>
+        </is>
+      </c>
+      <c r="O230" t="n">
+        <v>682928</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="n">
+        <v>0</v>
+      </c>
+      <c r="V230" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" t="n">
+        <v>0</v>
+      </c>
+      <c r="X230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Dylan Crews</t>
+        </is>
+      </c>
+      <c r="O231" t="n">
+        <v>686611</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
+      <c r="V231" t="n">
+        <v>0</v>
+      </c>
+      <c r="W231" t="n">
+        <v>0</v>
+      </c>
+      <c r="X231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Daylen Lile</t>
+        </is>
+      </c>
+      <c r="O232" t="n">
+        <v>695734</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="n">
+        <v>0</v>
+      </c>
+      <c r="V232" t="n">
+        <v>0</v>
+      </c>
+      <c r="W232" t="n">
+        <v>0</v>
+      </c>
+      <c r="X232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE232" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>José Tena</t>
+        </is>
+      </c>
+      <c r="O233" t="n">
+        <v>677588</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0</v>
+      </c>
+      <c r="V233" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" t="n">
+        <v>0</v>
+      </c>
+      <c r="X233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE233" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Jorbit Vivas</t>
+        </is>
+      </c>
+      <c r="O234" t="n">
+        <v>678391</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
+      <c r="V234" t="n">
+        <v>0</v>
+      </c>
+      <c r="W234" t="n">
+        <v>0</v>
+      </c>
+      <c r="X234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:51:33 AM PT</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>822708</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>10:35 AM PT</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
         <is>
           <t>Keibert Ruiz</t>
         </is>
       </c>
-      <c r="O226" t="n">
+      <c r="O235" t="n">
         <v>660688</v>
       </c>
-      <c r="P226" t="inlineStr">
+      <c r="P235" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr">
+      <c r="Q235" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R226" t="n">
-        <v>0</v>
-      </c>
-      <c r="S226" t="n">
-        <v>0</v>
-      </c>
-      <c r="T226" t="n">
-        <v>0</v>
-      </c>
-      <c r="U226" t="n">
-        <v>0</v>
-      </c>
-      <c r="V226" t="n">
-        <v>0</v>
-      </c>
-      <c r="W226" t="n">
-        <v>0</v>
-      </c>
-      <c r="X226" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y226" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z226" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA226" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB226" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC226" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD226" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE226" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF226" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG226" t="n">
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="n">
+        <v>0</v>
+      </c>
+      <c r="V235" t="n">
+        <v>0</v>
+      </c>
+      <c r="W235" t="n">
+        <v>0</v>
+      </c>
+      <c r="X235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG226"/>
-  <conditionalFormatting sqref="AE2:AE226">
+  <autoFilter ref="A1:AG235"/>
+  <conditionalFormatting sqref="AE2:AE235">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
         <v>1</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>2</v>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="H124" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" t="n">
         <v>1</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
       </c>
       <c r="J124" t="n">
         <v>2</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
         <v>1</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
       </c>
       <c r="J125" t="n">
         <v>2</v>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
         <v>1</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>2</v>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15016,10 +15016,10 @@
         </is>
       </c>
       <c r="H127" t="n">
+        <v>2</v>
+      </c>
+      <c r="I127" t="n">
         <v>1</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>2</v>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15139,10 +15139,10 @@
         </is>
       </c>
       <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
         <v>1</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
       </c>
       <c r="J128" t="n">
         <v>2</v>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
         <v>1</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>2</v>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15385,10 +15385,10 @@
         </is>
       </c>
       <c r="H130" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" t="n">
         <v>1</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>2</v>
@@ -15427,10 +15427,10 @@
         </is>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T130" t="n">
         <v>0</v>
@@ -15463,7 +15463,7 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE130" s="4" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
         <v>1</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>2</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="H168" t="n">
+        <v>2</v>
+      </c>
+      <c r="I168" t="n">
         <v>1</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
       </c>
       <c r="J168" t="n">
         <v>2</v>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19858,10 +19858,10 @@
         </is>
       </c>
       <c r="H169" t="n">
+        <v>2</v>
+      </c>
+      <c r="I169" t="n">
         <v>1</v>
-      </c>
-      <c r="I169" t="n">
-        <v>0</v>
       </c>
       <c r="J169" t="n">
         <v>2</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="H170" t="n">
+        <v>2</v>
+      </c>
+      <c r="I170" t="n">
         <v>1</v>
-      </c>
-      <c r="I170" t="n">
-        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>2</v>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20104,10 +20104,10 @@
         </is>
       </c>
       <c r="H171" t="n">
+        <v>2</v>
+      </c>
+      <c r="I171" t="n">
         <v>1</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>2</v>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 3 | 1 out</t>
+          <t>Top 3 | 2 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20227,10 +20227,10 @@
         </is>
       </c>
       <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="n">
         <v>1</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>2</v>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:35 AM PT</t>
+          <t>2026-07-12 09:53:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24513,7 +24513,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:34 AM PT</t>
+          <t>2026-07-12 09:53:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 09:51:33 AM PT</t>
+          <t>2026-07-12 09:53:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -463,7 +463,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -690,17 +690,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -813,17 +813,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -936,17 +936,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -14520,17 +14520,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14643,17 +14643,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14766,17 +14766,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14889,17 +14889,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15012,17 +15012,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15258,17 +15258,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15381,17 +15381,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -15504,17 +15504,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15550,10 +15550,10 @@
         </is>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
         <v>0</v>
@@ -15586,7 +15586,7 @@
         <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE131" s="4" t="n">
         <v>0</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -19731,17 +19731,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19854,17 +19854,17 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19977,17 +19977,17 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20100,17 +20100,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Top 3 | 2 out</t>
+          <t>Bottom 3 | 0 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20223,17 +20223,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:35 AM PT</t>
+          <t>2026-07-12 09:55:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24513,7 +24513,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:34 AM PT</t>
+          <t>2026-07-12 09:55:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 09:53:33 AM PT</t>
+          <t>2026-07-12 09:55:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14770,7 +14770,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14893,7 +14893,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15016,7 +15016,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19858,7 +19858,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -19900,10 +19900,10 @@
         </is>
       </c>
       <c r="R169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T169" t="n">
         <v>0</v>
@@ -19936,7 +19936,7 @@
         <v>0</v>
       </c>
       <c r="AD169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE169" s="4" t="n">
         <v>0</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20104,7 +20104,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 3 | 0 out</t>
+          <t>Bottom 3 | 1 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20227,7 +20227,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:35 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24513,7 +24513,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:34 AM PT</t>
+          <t>2026-07-12 09:57:35 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 09:55:33 AM PT</t>
+          <t>2026-07-12 09:57:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>4</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -1027,7 +1027,7 @@
         <v>4</v>
       </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>4</v>
       </c>
       <c r="AG5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1161,74 +1161,83 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>824574</v>
+        <v>823358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bryan Reynolds</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>668804</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Jacob Wilson</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>805779</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1255,16 +1264,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1284,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1316,20 +1325,20 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>811965</v>
+        <v>805779</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1389,7 +1398,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1430,20 +1439,20 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>669127</v>
+        <v>811965</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" t="n">
@@ -1503,7 +1512,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1544,20 +1553,20 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>641680</v>
+        <v>669127</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1617,7 +1626,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1658,20 +1667,20 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Colby Thomas</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>687515</v>
+        <v>641680</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1731,7 +1740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1772,20 +1781,20 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Joey Meneses</t>
+          <t>Colby Thomas</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>608841</v>
+        <v>687515</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1845,7 +1854,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1886,20 +1895,20 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Joey Meneses</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>671732</v>
+        <v>608841</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R12" t="n">
@@ -1959,7 +1968,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2000,20 +2009,20 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>703607</v>
+        <v>671732</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -2073,7 +2082,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2114,20 +2123,20 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>675961</v>
+        <v>703607</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -2187,15 +2196,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>823029</v>
+        <v>824574</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2218,30 +2227,30 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>686948</v>
+        <v>675961</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2301,7 +2310,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2342,20 +2351,20 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>645277</v>
+        <v>686948</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R16" t="n">
@@ -2415,7 +2424,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2456,20 +2465,20 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>621566</v>
+        <v>645277</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2529,7 +2538,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2570,20 +2579,20 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>671739</v>
+        <v>621566</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2643,7 +2652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2684,20 +2693,20 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>643289</v>
+        <v>671739</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2757,7 +2766,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2798,20 +2807,20 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>642086</v>
+        <v>643289</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2871,7 +2880,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2912,20 +2921,20 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>663586</v>
+        <v>642086</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -2985,7 +2994,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3026,20 +3035,20 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>805347</v>
+        <v>663586</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R22" t="n">
@@ -3099,7 +3108,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3140,20 +3149,20 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>676551</v>
+        <v>805347</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -3213,15 +3222,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>824814</v>
+        <v>823029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3239,35 +3248,35 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>683002</v>
+        <v>676551</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -3327,7 +3336,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3368,20 +3377,20 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>621493</v>
+        <v>683002</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -3441,7 +3450,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3482,20 +3491,20 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>687637</v>
+        <v>621493</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -3555,7 +3564,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3596,20 +3605,20 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>624413</v>
+        <v>687637</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -3669,7 +3678,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3710,20 +3719,20 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>694212</v>
+        <v>624413</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3783,7 +3792,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3824,20 +3833,20 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Blaze Alexander</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>677942</v>
+        <v>694212</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -3897,7 +3906,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3938,20 +3947,20 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Blaze Alexander</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>681297</v>
+        <v>677942</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -4011,7 +4020,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4052,20 +4061,20 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>665750</v>
+        <v>681297</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -4125,7 +4134,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4166,20 +4175,20 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>702616</v>
+        <v>665750</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -4239,15 +4248,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>823602</v>
+        <v>824814</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4265,26 +4274,26 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>678011</v>
+        <v>702616</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -4293,7 +4302,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -4353,7 +4362,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4394,20 +4403,20 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>678882</v>
+        <v>678011</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -4467,7 +4476,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4508,20 +4517,20 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>677800</v>
+        <v>678882</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -4581,7 +4590,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4622,20 +4631,20 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Romy Gonzalez</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>663853</v>
+        <v>677800</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -4695,7 +4704,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4736,20 +4745,20 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Romy Gonzalez</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>702332</v>
+        <v>663853</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -4809,7 +4818,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4850,20 +4859,20 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>655316</v>
+        <v>702332</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -4923,7 +4932,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4964,20 +4973,20 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>680776</v>
+        <v>655316</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -5037,7 +5046,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5078,20 +5087,20 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>681987</v>
+        <v>680776</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -5151,7 +5160,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5192,20 +5201,20 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>657136</v>
+        <v>681987</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -5265,11 +5274,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>824491</v>
+        <v>823602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5296,30 +5305,30 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>691718</v>
+        <v>657136</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -5379,7 +5388,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5420,20 +5429,20 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>673548</v>
+        <v>691718</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -5493,7 +5502,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5534,20 +5543,20 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>608324</v>
+        <v>673548</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -5607,7 +5616,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5648,20 +5657,20 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>608348</v>
+        <v>608324</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -5721,7 +5730,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5762,20 +5771,20 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>683737</v>
+        <v>608348</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -5835,7 +5844,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5876,20 +5885,20 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>663538</v>
+        <v>683737</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -5949,7 +5958,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5990,20 +5999,20 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>664023</v>
+        <v>663538</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -6063,7 +6072,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6104,20 +6113,20 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>621020</v>
+        <v>664023</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -6177,7 +6186,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6218,20 +6227,20 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Kevin Alcántara</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>682634</v>
+        <v>621020</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -6291,7 +6300,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6317,35 +6326,35 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Kevin Alcántara</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>682829</v>
+        <v>682634</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -6405,7 +6414,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6446,20 +6455,20 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>701398</v>
+        <v>682829</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -6519,7 +6528,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6560,20 +6569,20 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>668715</v>
+        <v>701398</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -6633,7 +6642,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6674,20 +6683,20 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>668709</v>
+        <v>668715</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R54" t="n">
@@ -6747,7 +6756,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6788,20 +6797,20 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>553993</v>
+        <v>668709</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -6861,7 +6870,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6902,20 +6911,20 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>663886</v>
+        <v>553993</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R56" t="n">
@@ -6975,7 +6984,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7016,20 +7025,20 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>682622</v>
+        <v>663886</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -7089,7 +7098,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7130,20 +7139,20 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Edwin Arroyo</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>695490</v>
+        <v>682622</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R58" t="n">
@@ -7203,7 +7212,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7244,20 +7253,20 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Edwin Arroyo</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>663647</v>
+        <v>695490</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -7317,11 +7326,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>823842</v>
+        <v>824491</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,35 +7352,35 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>683953</v>
+        <v>663647</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R60" t="n">
@@ -7431,7 +7440,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7472,20 +7481,20 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>677587</v>
+        <v>683953</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R61" t="n">
@@ -7545,7 +7554,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7586,20 +7595,20 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>800050</v>
+        <v>677587</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -7659,7 +7668,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7700,20 +7709,20 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>700932</v>
+        <v>800050</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -7773,7 +7782,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7814,20 +7823,20 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -7887,7 +7896,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7928,20 +7937,20 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>672356</v>
+        <v>696135</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -8001,7 +8010,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8042,20 +8051,20 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>690984</v>
+        <v>672356</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R66" t="n">
@@ -8115,7 +8124,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8156,20 +8165,20 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>672275</v>
+        <v>690984</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8229,7 +8238,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8270,20 +8279,20 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>680757</v>
+        <v>672275</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R68" t="n">
@@ -8343,15 +8352,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>824574</v>
+        <v>823842</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8369,26 +8378,26 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>803011</v>
+        <v>680757</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -8397,7 +8406,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -8457,7 +8466,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8498,20 +8507,20 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>808959</v>
+        <v>803011</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -8571,7 +8580,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8612,20 +8621,20 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>678246</v>
+        <v>808959</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8685,7 +8694,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8726,20 +8735,20 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>695657</v>
+        <v>678246</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -8799,7 +8808,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8840,20 +8849,20 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>643217</v>
+        <v>695657</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -8913,7 +8922,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8954,20 +8963,20 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>691019</v>
+        <v>643217</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -9027,7 +9036,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9068,20 +9077,20 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>695731</v>
+        <v>691019</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -9141,7 +9150,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9182,20 +9191,20 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>671976</v>
+        <v>695731</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R76" t="n">
@@ -9255,7 +9264,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9296,20 +9305,20 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>805367</v>
+        <v>671976</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9369,15 +9378,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>824250</v>
+        <v>824574</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9400,30 +9409,30 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>805808</v>
+        <v>805367</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R78" t="n">
@@ -9483,7 +9492,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9524,20 +9533,20 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>693307</v>
+        <v>805808</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -9597,7 +9606,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9638,20 +9647,20 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>690993</v>
+        <v>693307</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R80" t="n">
@@ -9711,7 +9720,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9752,20 +9761,20 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>682985</v>
+        <v>690993</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -9825,7 +9834,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9866,20 +9875,20 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>679529</v>
+        <v>682985</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R82" t="n">
@@ -9939,7 +9948,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -9980,20 +9989,20 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Kerry Carpenter</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>681481</v>
+        <v>679529</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -10053,7 +10062,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10094,20 +10103,20 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Kerry Carpenter</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>656716</v>
+        <v>681481</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R84" t="n">
@@ -10167,7 +10176,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10208,20 +10217,20 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>663837</v>
+        <v>656716</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -10281,7 +10290,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10322,20 +10331,20 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>681546</v>
+        <v>663837</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R86" t="n">
@@ -10395,15 +10404,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>822876</v>
+        <v>824250</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -10421,35 +10430,35 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>665161</v>
+        <v>681546</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -10509,7 +10518,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10550,20 +10559,20 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>670541</v>
+        <v>665161</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R88" t="n">
@@ -10623,7 +10632,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10664,20 +10673,20 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>670623</v>
+        <v>670541</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R89" t="n">
@@ -10737,7 +10746,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10778,20 +10787,20 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>572233</v>
+        <v>670623</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R90" t="n">
@@ -10851,7 +10860,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10892,20 +10901,20 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>514888</v>
+        <v>572233</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -10965,7 +10974,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11006,20 +11015,20 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>701358</v>
+        <v>514888</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R92" t="n">
@@ -11079,7 +11088,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11120,20 +11129,20 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>664774</v>
+        <v>701358</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -11193,7 +11202,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11234,20 +11243,20 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Brice Matthews</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>694728</v>
+        <v>664774</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R94" t="n">
@@ -11307,7 +11316,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11348,20 +11357,20 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Brice Matthews</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>543877</v>
+        <v>694728</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -11421,15 +11430,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>824814</v>
+        <v>822876</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11452,21 +11461,21 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>695600</v>
+        <v>543877</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -11475,7 +11484,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R96" t="n">
@@ -11535,7 +11544,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11576,20 +11585,20 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>677951</v>
+        <v>695600</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R97" t="n">
@@ -11649,7 +11658,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11690,20 +11699,20 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>695506</v>
+        <v>677951</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R98" t="n">
@@ -11763,7 +11772,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11804,20 +11813,20 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>657041</v>
+        <v>695506</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -11877,7 +11886,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11918,20 +11927,20 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>686469</v>
+        <v>657041</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R100" t="n">
@@ -11991,7 +12000,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12032,20 +12041,20 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>521692</v>
+        <v>686469</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R101" t="n">
@@ -12105,7 +12114,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12146,20 +12155,20 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>686681</v>
+        <v>521692</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R102" t="n">
@@ -12219,7 +12228,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12260,20 +12269,20 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Josh Rojas</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>668942</v>
+        <v>686681</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -12333,7 +12342,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12374,20 +12383,20 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Rojas</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>686555</v>
+        <v>668942</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -12447,15 +12456,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>823681</v>
+        <v>824814</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -12478,30 +12487,30 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>687263</v>
+        <v>686555</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -12561,7 +12570,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12602,20 +12611,20 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>545361</v>
+        <v>687263</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R106" t="n">
@@ -12675,7 +12684,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12716,20 +12725,20 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>694384</v>
+        <v>545361</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -12789,7 +12798,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12830,20 +12839,20 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>624585</v>
+        <v>694384</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R108" t="n">
@@ -12903,7 +12912,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12944,20 +12953,20 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>666176</v>
+        <v>624585</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -13017,7 +13026,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13058,20 +13067,20 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>666139</v>
+        <v>666176</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R110" t="n">
@@ -13131,7 +13140,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13172,20 +13181,20 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>672724</v>
+        <v>666139</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -13245,7 +13254,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13286,20 +13295,20 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>694203</v>
+        <v>672724</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R112" t="n">
@@ -13359,7 +13368,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13400,20 +13409,20 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>681351</v>
+        <v>694203</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -13473,15 +13482,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>823842</v>
+        <v>823681</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13499,35 +13508,35 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>672640</v>
+        <v>681351</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R114" t="n">
@@ -13587,7 +13596,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13628,20 +13637,20 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>681715</v>
+        <v>672640</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -13701,7 +13710,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13742,20 +13751,20 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>689414</v>
+        <v>681715</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R116" t="n">
@@ -13815,7 +13824,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13856,20 +13865,20 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>669364</v>
+        <v>689414</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -13929,7 +13938,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -13970,20 +13979,20 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>691594</v>
+        <v>669364</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -14043,7 +14052,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14084,20 +14093,20 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Leo Jiménez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>677870</v>
+        <v>691594</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -14157,7 +14166,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14198,20 +14207,20 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Leo Jiménez</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>665923</v>
+        <v>677870</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R120" t="n">
@@ -14271,7 +14280,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14312,20 +14321,20 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Rece Hinds</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>677956</v>
+        <v>665923</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -14385,7 +14394,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14426,20 +14435,20 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>640459</v>
+        <v>677956</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R122" t="n">
@@ -14499,77 +14508,68 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>823358</v>
+        <v>823842</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
-        <v>1</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>592885</v>
+        <v>640459</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
         <v>0</v>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -14672,20 +14672,20 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>694192</v>
+        <v>592885</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R124" t="n">
@@ -14725,7 +14725,7 @@
         <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE124" s="4" t="n">
         <v>0</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14770,7 +14770,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -14795,20 +14795,20 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>668930</v>
+        <v>694192</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -14848,7 +14848,7 @@
         <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE125" s="4" t="n">
         <v>0</v>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14893,7 +14893,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -14918,20 +14918,20 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>641343</v>
+        <v>668930</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R126" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15016,7 +15016,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -15041,20 +15041,20 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>596142</v>
+        <v>641343</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -15164,20 +15164,20 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>669003</v>
+        <v>596142</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R128" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -15287,20 +15287,20 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>686217</v>
+        <v>669003</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R129" t="n">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -15410,20 +15410,20 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>687401</v>
+        <v>686217</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R130" t="n">
@@ -15463,7 +15463,7 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE130" s="4" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -15533,20 +15533,20 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Braden Shewmake</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>669699</v>
+        <v>687401</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R131" t="n">
@@ -15606,68 +15606,77 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>823681</v>
+        <v>823358</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>2</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Braden Shewmake</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>669699</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>Trevor Larnach</t>
-        </is>
-      </c>
-      <c r="O132" t="n">
-        <v>663616</v>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>LF</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T132" t="n">
         <v>0</v>
@@ -15700,7 +15709,7 @@
         <v>0</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE132" s="4" t="n">
         <v>0</v>
@@ -15720,7 +15729,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15761,20 +15770,20 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>680777</v>
+        <v>663616</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R133" t="n">
@@ -15834,7 +15843,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15875,20 +15884,20 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>605137</v>
+        <v>680777</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R134" t="n">
@@ -15948,7 +15957,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -15989,20 +15998,20 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>665019</v>
+        <v>605137</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -16062,7 +16071,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16103,20 +16112,20 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>668904</v>
+        <v>665019</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R136" t="n">
@@ -16176,7 +16185,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16217,20 +16226,20 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>686797</v>
+        <v>668904</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R137" t="n">
@@ -16290,7 +16299,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16331,20 +16340,20 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Alan Roden</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>702176</v>
+        <v>686797</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R138" t="n">
@@ -16404,7 +16413,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16445,20 +16454,20 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Alan Roden</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>807712</v>
+        <v>702176</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -16518,7 +16527,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16559,20 +16568,20 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>668952</v>
+        <v>807712</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R140" t="n">
@@ -16632,15 +16641,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>823602</v>
+        <v>823681</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -16663,30 +16672,30 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>A.J. Ewing</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>805999</v>
+        <v>668952</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -16746,7 +16755,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16787,20 +16796,20 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>A.J. Ewing</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>665742</v>
+        <v>805999</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R142" t="n">
@@ -16860,7 +16869,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16901,20 +16910,20 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>596019</v>
+        <v>665742</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -16974,7 +16983,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17015,20 +17024,20 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Eric Wagaman</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>676572</v>
+        <v>596019</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R144" t="n">
@@ -17088,7 +17097,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17129,20 +17138,20 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Eric Wagaman</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>701807</v>
+        <v>676572</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R145" t="n">
@@ -17202,7 +17211,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17243,20 +17252,20 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Tyrone Taylor</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>621438</v>
+        <v>701807</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R146" t="n">
@@ -17316,7 +17325,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17357,20 +17366,20 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Luis Torrens</t>
+          <t>Tyrone Taylor</t>
         </is>
       </c>
       <c r="O147" t="n">
-        <v>620443</v>
+        <v>621438</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -17430,7 +17439,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17471,20 +17480,20 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Luis Torrens</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>683146</v>
+        <v>620443</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R148" t="n">
@@ -17544,7 +17553,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17585,20 +17594,20 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Zack Short</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="O149" t="n">
-        <v>670097</v>
+        <v>683146</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R149" t="n">
@@ -17658,15 +17667,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>822708</v>
+        <v>823602</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -17684,35 +17693,35 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Zack Short</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>663757</v>
+        <v>670097</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R150" t="n">
@@ -17772,7 +17781,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17813,20 +17822,20 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="O151" t="n">
-        <v>700250</v>
+        <v>663757</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R151" t="n">
@@ -17886,7 +17895,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17927,20 +17936,20 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Jasson Domínguez</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="O152" t="n">
-        <v>691176</v>
+        <v>700250</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R152" t="n">
@@ -18000,7 +18009,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18041,20 +18050,20 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Jasson Domínguez</t>
         </is>
       </c>
       <c r="O153" t="n">
-        <v>641355</v>
+        <v>691176</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R153" t="n">
@@ -18114,7 +18123,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18155,20 +18164,20 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="O154" t="n">
-        <v>665862</v>
+        <v>641355</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R154" t="n">
@@ -18228,7 +18237,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18269,20 +18278,20 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>José Caballero</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="O155" t="n">
-        <v>676609</v>
+        <v>665862</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R155" t="n">
@@ -18342,7 +18351,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18383,20 +18392,20 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="O156" t="n">
-        <v>641857</v>
+        <v>676609</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R156" t="n">
@@ -18456,7 +18465,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18497,20 +18506,20 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="O157" t="n">
-        <v>669224</v>
+        <v>641857</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R157" t="n">
@@ -18570,7 +18579,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18611,20 +18620,20 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Max Schuemann</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="O158" t="n">
-        <v>680474</v>
+        <v>669224</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R158" t="n">
@@ -18684,15 +18693,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>824250</v>
+        <v>822708</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -18715,30 +18724,30 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Max Schuemann</t>
         </is>
       </c>
       <c r="O159" t="n">
-        <v>607208</v>
+        <v>680474</v>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R159" t="n">
@@ -18798,7 +18807,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18839,20 +18848,20 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="O160" t="n">
-        <v>656941</v>
+        <v>607208</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R160" t="n">
@@ -18912,7 +18921,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -18953,20 +18962,20 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="O161" t="n">
-        <v>547180</v>
+        <v>656941</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R161" t="n">
@@ -19026,7 +19035,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19067,20 +19076,20 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="O162" t="n">
-        <v>664761</v>
+        <v>547180</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R162" t="n">
@@ -19140,7 +19149,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19181,20 +19190,20 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="O163" t="n">
-        <v>624641</v>
+        <v>664761</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R163" t="n">
@@ -19254,7 +19263,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19295,20 +19304,20 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="O164" t="n">
-        <v>669016</v>
+        <v>624641</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R164" t="n">
@@ -19368,7 +19377,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19409,20 +19418,20 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="O165" t="n">
-        <v>656537</v>
+        <v>669016</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R165" t="n">
@@ -19482,7 +19491,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19523,20 +19532,20 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="O166" t="n">
-        <v>592663</v>
+        <v>656537</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R166" t="n">
@@ -19596,7 +19605,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19637,20 +19646,20 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="O167" t="n">
-        <v>681082</v>
+        <v>592663</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R167" t="n">
@@ -19710,77 +19719,68 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>823358</v>
+        <v>824250</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H168" t="n">
-        <v>1</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" t="n">
-        <v>0</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="O168" t="n">
-        <v>663968</v>
+        <v>681082</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T168" t="n">
         <v>0</v>
@@ -19819,10 +19819,10 @@
         <v>0</v>
       </c>
       <c r="AF168" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG168" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19858,7 +19858,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -19883,20 +19883,20 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="O169" t="n">
-        <v>664040</v>
+        <v>663968</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R169" t="n">
@@ -19936,7 +19936,7 @@
         <v>0</v>
       </c>
       <c r="AD169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE169" s="4" t="n">
         <v>0</v>
@@ -19945,7 +19945,7 @@
         <v>4</v>
       </c>
       <c r="AG169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -20006,27 +20006,27 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="O170" t="n">
-        <v>668804</v>
+        <v>664040</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T170" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="AD170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE170" s="4" t="n">
         <v>0</v>
@@ -20068,7 +20068,7 @@
         <v>4</v>
       </c>
       <c r="AG170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20104,7 +20104,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -20191,7 +20191,7 @@
         <v>4</v>
       </c>
       <c r="AG171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 3 | 1 out</t>
+          <t>Bottom 3 | 2 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20227,7 +20227,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -20314,7 +20314,7 @@
         <v>4</v>
       </c>
       <c r="AG172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24513,7 +24513,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:34 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:35 AM PT</t>
+          <t>2026-07-12 09:59:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 09:57:33 AM PT</t>
+          <t>2026-07-12 09:59:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14653,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14776,7 +14776,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14899,7 +14899,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15022,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15145,7 +15145,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15268,7 +15268,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15391,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15637,7 +15637,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17097,7 +17097,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17325,7 +17325,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19864,7 +19864,7 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19987,7 +19987,7 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20110,7 +20110,7 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20233,7 +20233,7 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:35 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24513,7 +24513,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:34 AM PT</t>
+          <t>2026-07-12 10:01:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 09:59:33 AM PT</t>
+          <t>2026-07-12 10:01:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -88,6 +93,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -669,7 +675,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -697,10 +703,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -792,7 +798,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -820,10 +826,10 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -859,7 +865,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -888,8 +894,8 @@
       <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
+      <c r="AB3" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -898,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
@@ -915,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -943,10 +949,10 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1038,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1066,10 +1072,10 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1161,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1189,10 +1195,10 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1284,7 +1290,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1398,7 +1404,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1512,7 +1518,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1626,7 +1632,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1740,7 +1746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1854,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1968,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2082,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2196,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2310,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2424,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2538,7 +2544,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2652,7 +2658,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2766,7 +2772,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2880,7 +2886,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2994,7 +3000,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3108,7 +3114,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3222,7 +3228,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3336,7 +3342,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3450,7 +3456,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3564,7 +3570,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3678,7 +3684,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3792,7 +3798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3906,7 +3912,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4020,7 +4026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4134,7 +4140,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4248,7 +4254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4362,7 +4368,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4476,7 +4482,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4590,7 +4596,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4704,7 +4710,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4818,7 +4824,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4932,7 +4938,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5046,7 +5052,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5160,7 +5166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5274,7 +5280,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5388,7 +5394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5502,7 +5508,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5616,7 +5622,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5730,7 +5736,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5844,7 +5850,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5958,7 +5964,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6072,7 +6078,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6186,7 +6192,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6300,7 +6306,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6414,7 +6420,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6528,7 +6534,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6642,7 +6648,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6756,7 +6762,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6870,7 +6876,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6984,7 +6990,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7098,7 +7104,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7212,7 +7218,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7326,7 +7332,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7440,7 +7446,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7554,7 +7560,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7668,7 +7674,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7782,7 +7788,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7896,7 +7902,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8010,7 +8016,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8124,7 +8130,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8238,7 +8244,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8352,7 +8358,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8466,7 +8472,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8580,7 +8586,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8694,7 +8700,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8808,7 +8814,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8922,7 +8928,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9036,7 +9042,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9150,7 +9156,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9264,7 +9270,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9378,7 +9384,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9492,7 +9498,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9606,7 +9612,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9720,7 +9726,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9834,7 +9840,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9948,7 +9954,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10062,7 +10068,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10176,7 +10182,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10290,7 +10296,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10404,7 +10410,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10518,7 +10524,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10632,7 +10638,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10746,7 +10752,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10860,7 +10866,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10974,7 +10980,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11088,7 +11094,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11202,7 +11208,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11316,7 +11322,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11430,7 +11436,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11544,7 +11550,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11658,7 +11664,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11772,7 +11778,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11886,7 +11892,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12000,7 +12006,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12114,7 +12120,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12228,7 +12234,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12342,7 +12348,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12456,7 +12462,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12570,7 +12576,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12684,7 +12690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12798,7 +12804,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12912,7 +12918,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13026,7 +13032,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13140,7 +13146,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13254,7 +13260,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13368,7 +13374,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13482,7 +13488,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13596,7 +13602,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13710,7 +13716,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13824,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13938,7 +13944,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14052,7 +14058,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14166,7 +14172,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14280,7 +14286,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14394,7 +14400,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14508,7 +14514,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14622,7 +14628,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14650,10 +14656,10 @@
         <v>2</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -14745,7 +14751,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14773,10 +14779,10 @@
         <v>2</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14868,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14896,10 +14902,10 @@
         <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -14991,7 +14997,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15019,10 +15025,10 @@
         <v>2</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15114,7 +15120,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15142,10 +15148,10 @@
         <v>2</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15237,7 +15243,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15265,10 +15271,10 @@
         <v>2</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15360,7 +15366,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15388,10 +15394,10 @@
         <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15483,7 +15489,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15511,10 +15517,10 @@
         <v>2</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15606,7 +15612,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15634,10 +15640,10 @@
         <v>2</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -15729,7 +15735,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15843,7 +15849,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15957,7 +15963,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16071,7 +16077,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16185,7 +16191,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16299,7 +16305,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16413,7 +16419,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16527,7 +16533,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16641,7 +16647,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16755,7 +16761,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16869,7 +16875,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16983,7 +16989,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17097,7 +17103,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17211,7 +17217,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17325,7 +17331,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17439,7 +17445,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17553,7 +17559,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17667,7 +17673,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17781,7 +17787,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17895,7 +17901,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18009,7 +18015,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18123,7 +18129,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18237,7 +18243,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18351,7 +18357,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18465,7 +18471,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18579,7 +18585,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18693,7 +18699,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18807,7 +18813,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18921,7 +18927,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19035,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19149,7 +19155,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19263,7 +19269,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19377,7 +19383,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19491,7 +19497,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19605,7 +19611,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19719,7 +19725,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19833,7 +19839,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19861,10 +19867,10 @@
         <v>2</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -19956,7 +19962,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19984,10 +19990,10 @@
         <v>2</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20079,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20107,10 +20113,10 @@
         <v>2</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20202,7 +20208,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20230,10 +20236,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20325,7 +20331,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20431,7 +20437,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20537,7 +20543,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20643,7 +20649,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20749,7 +20755,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20855,7 +20861,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20961,7 +20967,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21067,7 +21073,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21173,7 +21179,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21279,7 +21285,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21393,7 +21399,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21507,7 +21513,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21621,7 +21627,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21735,7 +21741,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21849,7 +21855,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21963,7 +21969,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22077,7 +22083,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22191,7 +22197,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22305,7 +22311,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22411,7 +22417,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22517,7 +22523,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22623,7 +22629,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22729,7 +22735,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22835,7 +22841,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22941,7 +22947,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23047,7 +23053,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23153,7 +23159,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23259,7 +23265,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23373,7 +23379,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23487,7 +23493,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23601,7 +23607,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23715,7 +23721,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23829,7 +23835,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23943,7 +23949,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24057,7 +24063,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24171,7 +24177,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24285,7 +24291,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24399,7 +24405,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24513,7 +24519,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24627,7 +24633,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24741,7 +24747,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24855,7 +24861,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24969,7 +24975,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25083,7 +25089,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25197,7 +25203,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25311,7 +25317,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25425,7 +25431,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25539,7 +25545,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25653,7 +25659,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25767,7 +25773,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25881,7 +25887,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -25995,7 +26001,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26109,7 +26115,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26223,7 +26229,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:34 AM PT</t>
+          <t>2026-07-12 10:03:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26337,7 +26343,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26451,7 +26457,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26565,7 +26571,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26679,7 +26685,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26793,7 +26799,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26907,7 +26913,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27021,7 +27027,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27135,7 +27141,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27249,7 +27255,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:01:33 AM PT</t>
+          <t>2026-07-12 10:03:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27387,12 +27393,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Stat Type</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I124" t="n">
         <v>2</v>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14776,7 +14776,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I125" t="n">
         <v>2</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I126" t="n">
         <v>2</v>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
         <v>2</v>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I128" t="n">
         <v>2</v>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I129" t="n">
         <v>2</v>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -15391,7 +15391,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I130" t="n">
         <v>2</v>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I131" t="n">
         <v>2</v>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I132" t="n">
         <v>2</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18813,7 +18813,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -19864,7 +19864,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I169" t="n">
         <v>2</v>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I170" t="n">
         <v>2</v>
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -20110,7 +20110,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
         <v>2</v>
@@ -20152,10 +20152,10 @@
         </is>
       </c>
       <c r="R171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T171" t="n">
         <v>0</v>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20221,7 +20221,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 3 | 2 out</t>
+          <t>Bottom 3 | 3 out</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -20233,7 +20233,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
         <v>2</v>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:35 AM PT</t>
+          <t>2026-07-12 10:05:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21627,7 +21627,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22311,7 +22311,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23721,7 +23721,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24291,7 +24291,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24405,7 +24405,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24747,7 +24747,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24975,7 +24975,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25317,7 +25317,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25545,7 +25545,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25887,7 +25887,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26001,7 +26001,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26115,7 +26115,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:34 AM PT</t>
+          <t>2026-07-12 10:05:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26343,7 +26343,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26685,7 +26685,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26799,7 +26799,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26913,7 +26913,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27141,7 +27141,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27255,7 +27255,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:03:33 AM PT</t>
+          <t>2026-07-12 10:05:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -469,7 +469,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -688,22 +688,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -811,22 +811,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -934,22 +934,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1180,57 +1180,57 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>668804</v>
+        <v>592885</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1243,11 +1243,11 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
@@ -1270,16 +1270,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1</v>
-      </c>
-      <c r="AE6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1290,74 +1290,83 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>824574</v>
+        <v>823358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bryan Reynolds</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>668804</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Jacob Wilson</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>805779</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1384,16 +1393,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1404,7 +1413,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1445,20 +1454,20 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>811965</v>
+        <v>805779</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" t="n">
@@ -1518,7 +1527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1559,20 +1568,20 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>669127</v>
+        <v>811965</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1632,7 +1641,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1673,20 +1682,20 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>641680</v>
+        <v>669127</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1746,7 +1755,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1787,20 +1796,20 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Colby Thomas</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>687515</v>
+        <v>641680</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1860,7 +1869,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1901,20 +1910,20 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Joey Meneses</t>
+          <t>Colby Thomas</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>608841</v>
+        <v>687515</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R12" t="n">
@@ -1974,7 +1983,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2015,20 +2024,20 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Joey Meneses</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>671732</v>
+        <v>608841</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -2088,7 +2097,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2129,20 +2138,20 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>703607</v>
+        <v>671732</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -2202,7 +2211,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2243,20 +2252,20 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>675961</v>
+        <v>703607</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2316,15 +2325,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>823029</v>
+        <v>824574</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2347,30 +2356,30 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>686948</v>
+        <v>675961</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R16" t="n">
@@ -2430,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2471,20 +2480,20 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>645277</v>
+        <v>686948</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2544,7 +2553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2585,20 +2594,20 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>621566</v>
+        <v>645277</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2658,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2699,20 +2708,20 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>671739</v>
+        <v>621566</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2772,7 +2781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2813,20 +2822,20 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>643289</v>
+        <v>671739</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2886,7 +2895,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2927,20 +2936,20 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>642086</v>
+        <v>643289</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -3000,7 +3009,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3041,20 +3050,20 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>663586</v>
+        <v>642086</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R22" t="n">
@@ -3114,7 +3123,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3155,20 +3164,20 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>805347</v>
+        <v>663586</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -3228,7 +3237,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3269,20 +3278,20 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>676551</v>
+        <v>805347</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -3342,15 +3351,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>824814</v>
+        <v>823029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3368,35 +3377,35 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>683002</v>
+        <v>676551</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -3456,7 +3465,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3469,7 +3478,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3480,6 +3489,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Home</t>
@@ -3497,20 +3515,20 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>621493</v>
+        <v>683002</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -3570,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3583,7 +3601,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3594,6 +3612,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Home</t>
@@ -3611,20 +3638,20 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>687637</v>
+        <v>621493</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -3684,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3697,7 +3724,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3708,6 +3735,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Home</t>
@@ -3725,20 +3761,20 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>624413</v>
+        <v>687637</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3798,7 +3834,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3811,7 +3847,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3822,6 +3858,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Home</t>
@@ -3839,20 +3884,20 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>694212</v>
+        <v>624413</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -3912,7 +3957,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3925,7 +3970,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3936,6 +3981,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Home</t>
@@ -3953,20 +4007,20 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Blaze Alexander</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>677942</v>
+        <v>694212</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -4026,7 +4080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4039,7 +4093,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4050,6 +4104,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Home</t>
@@ -4067,20 +4130,20 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Blaze Alexander</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>681297</v>
+        <v>677942</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -4140,7 +4203,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4153,7 +4216,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4164,6 +4227,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Home</t>
@@ -4181,20 +4253,20 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>665750</v>
+        <v>681297</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -4254,7 +4326,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4267,7 +4339,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4278,6 +4350,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Home</t>
@@ -4295,20 +4376,20 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>702616</v>
+        <v>665750</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -4368,20 +4449,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>823602</v>
+        <v>824814</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4392,28 +4473,37 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>678011</v>
+        <v>702616</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -4422,7 +4512,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -4482,7 +4572,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4523,20 +4613,20 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>678882</v>
+        <v>678011</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -4596,7 +4686,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4637,20 +4727,20 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>677800</v>
+        <v>678882</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -4710,7 +4800,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4751,20 +4841,20 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Romy Gonzalez</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>663853</v>
+        <v>677800</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -4824,7 +4914,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4865,20 +4955,20 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Romy Gonzalez</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>702332</v>
+        <v>663853</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -4938,7 +5028,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4979,20 +5069,20 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>655316</v>
+        <v>702332</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -5052,7 +5142,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5093,20 +5183,20 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>680776</v>
+        <v>655316</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -5166,7 +5256,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5207,20 +5297,20 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>681987</v>
+        <v>680776</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -5280,7 +5370,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5321,20 +5411,20 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>657136</v>
+        <v>681987</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -5394,11 +5484,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>824491</v>
+        <v>823602</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5425,30 +5515,30 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>691718</v>
+        <v>657136</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -5508,7 +5598,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5549,20 +5639,20 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>673548</v>
+        <v>691718</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -5622,7 +5712,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5663,20 +5753,20 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>608324</v>
+        <v>673548</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -5736,7 +5826,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5777,20 +5867,20 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>608348</v>
+        <v>608324</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -5850,7 +5940,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5891,20 +5981,20 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>683737</v>
+        <v>608348</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -5964,7 +6054,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6005,20 +6095,20 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>663538</v>
+        <v>683737</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -6078,7 +6168,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6119,20 +6209,20 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>664023</v>
+        <v>663538</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -6192,7 +6282,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6233,20 +6323,20 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>621020</v>
+        <v>664023</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -6306,7 +6396,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6347,20 +6437,20 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Kevin Alcántara</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>682634</v>
+        <v>621020</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -6420,7 +6510,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6446,35 +6536,35 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Kevin Alcántara</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>682829</v>
+        <v>682634</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -6534,7 +6624,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6575,20 +6665,20 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>701398</v>
+        <v>682829</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -6648,7 +6738,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6689,20 +6779,20 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>668715</v>
+        <v>701398</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R54" t="n">
@@ -6762,7 +6852,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6803,20 +6893,20 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>668709</v>
+        <v>668715</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -6876,7 +6966,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6917,20 +7007,20 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>553993</v>
+        <v>668709</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R56" t="n">
@@ -6990,7 +7080,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7031,20 +7121,20 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>663886</v>
+        <v>553993</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -7104,7 +7194,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7145,20 +7235,20 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>682622</v>
+        <v>663886</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R58" t="n">
@@ -7218,7 +7308,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7259,20 +7349,20 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Edwin Arroyo</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>695490</v>
+        <v>682622</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -7332,7 +7422,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7373,20 +7463,20 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Edwin Arroyo</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>663647</v>
+        <v>695490</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R60" t="n">
@@ -7446,11 +7536,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>823842</v>
+        <v>824491</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7472,35 +7562,35 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>683953</v>
+        <v>663647</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R61" t="n">
@@ -7560,7 +7650,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7601,20 +7691,20 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>677587</v>
+        <v>683953</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -7674,7 +7764,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7715,20 +7805,20 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>800050</v>
+        <v>677587</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -7788,7 +7878,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7829,20 +7919,20 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>700932</v>
+        <v>800050</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -7902,7 +7992,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -7943,20 +8033,20 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -8016,7 +8106,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8057,20 +8147,20 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>672356</v>
+        <v>696135</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R66" t="n">
@@ -8130,7 +8220,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8171,20 +8261,20 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>690984</v>
+        <v>672356</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8244,7 +8334,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8285,20 +8375,20 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>672275</v>
+        <v>690984</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R68" t="n">
@@ -8358,7 +8448,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8399,20 +8489,20 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>680757</v>
+        <v>672275</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -8472,15 +8562,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>824574</v>
+        <v>823842</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8498,26 +8588,26 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>803011</v>
+        <v>680757</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -8526,7 +8616,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -8586,7 +8676,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8627,20 +8717,20 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>808959</v>
+        <v>803011</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8700,7 +8790,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8741,20 +8831,20 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>678246</v>
+        <v>808959</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -8814,7 +8904,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8855,20 +8945,20 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>695657</v>
+        <v>678246</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -8928,7 +9018,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -8969,20 +9059,20 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>643217</v>
+        <v>695657</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -9042,7 +9132,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9083,20 +9173,20 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>691019</v>
+        <v>643217</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -9156,7 +9246,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9197,20 +9287,20 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>695731</v>
+        <v>691019</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R76" t="n">
@@ -9270,7 +9360,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9311,20 +9401,20 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>671976</v>
+        <v>695731</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9384,7 +9474,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9425,20 +9515,20 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>805367</v>
+        <v>671976</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R78" t="n">
@@ -9498,15 +9588,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>824250</v>
+        <v>824574</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9529,30 +9619,30 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>805808</v>
+        <v>805367</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -9612,7 +9702,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9653,20 +9743,20 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>693307</v>
+        <v>805808</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R80" t="n">
@@ -9726,7 +9816,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9767,20 +9857,20 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>690993</v>
+        <v>693307</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -9840,7 +9930,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9881,20 +9971,20 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>682985</v>
+        <v>690993</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R82" t="n">
@@ -9954,7 +10044,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -9995,20 +10085,20 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>679529</v>
+        <v>682985</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -10068,7 +10158,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10109,20 +10199,20 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Kerry Carpenter</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>681481</v>
+        <v>679529</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R84" t="n">
@@ -10182,7 +10272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10223,20 +10313,20 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Kerry Carpenter</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>656716</v>
+        <v>681481</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -10296,7 +10386,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10337,20 +10427,20 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>663837</v>
+        <v>656716</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R86" t="n">
@@ -10410,7 +10500,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10451,20 +10541,20 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>681546</v>
+        <v>663837</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -10524,15 +10614,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>822876</v>
+        <v>824250</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10550,35 +10640,35 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>665161</v>
+        <v>681546</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R88" t="n">
@@ -10638,7 +10728,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10679,20 +10769,20 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>670541</v>
+        <v>665161</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R89" t="n">
@@ -10752,7 +10842,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10793,20 +10883,20 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>670623</v>
+        <v>670541</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R90" t="n">
@@ -10866,7 +10956,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10907,20 +10997,20 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>572233</v>
+        <v>670623</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -10980,7 +11070,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11021,20 +11111,20 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>514888</v>
+        <v>572233</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R92" t="n">
@@ -11094,7 +11184,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11135,20 +11225,20 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>701358</v>
+        <v>514888</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -11208,7 +11298,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11249,20 +11339,20 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>664774</v>
+        <v>701358</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R94" t="n">
@@ -11322,7 +11412,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11363,20 +11453,20 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Brice Matthews</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>694728</v>
+        <v>664774</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -11436,7 +11526,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11477,20 +11567,20 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Brice Matthews</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>543877</v>
+        <v>694728</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R96" t="n">
@@ -11550,15 +11640,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>824814</v>
+        <v>822876</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -11581,21 +11671,21 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>695600</v>
+        <v>543877</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -11604,7 +11694,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R97" t="n">
@@ -11664,7 +11754,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11677,7 +11767,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -11688,6 +11778,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Away</t>
@@ -11705,20 +11804,20 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>677951</v>
+        <v>695600</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R98" t="n">
@@ -11778,7 +11877,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11791,7 +11890,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -11802,6 +11901,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>Away</t>
@@ -11819,20 +11927,20 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>695506</v>
+        <v>677951</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -11892,7 +12000,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11905,7 +12013,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -11916,6 +12024,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>Away</t>
@@ -11933,20 +12050,20 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>657041</v>
+        <v>695506</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R100" t="n">
@@ -12006,7 +12123,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12019,7 +12136,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -12030,6 +12147,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12047,20 +12173,20 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>686469</v>
+        <v>657041</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R101" t="n">
@@ -12120,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12133,7 +12259,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -12144,6 +12270,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12161,20 +12296,20 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>521692</v>
+        <v>686469</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R102" t="n">
@@ -12234,7 +12369,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12247,7 +12382,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -12258,6 +12393,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12275,20 +12419,20 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>686681</v>
+        <v>521692</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -12348,7 +12492,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12361,7 +12505,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -12372,6 +12516,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12389,20 +12542,20 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Josh Rojas</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>668942</v>
+        <v>686681</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -12462,7 +12615,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12475,7 +12628,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -12486,6 +12639,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12503,20 +12665,20 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Rojas</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>686555</v>
+        <v>668942</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -12576,20 +12738,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>823681</v>
+        <v>824814</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -12600,6 +12762,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12607,30 +12778,30 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>687263</v>
+        <v>686555</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R106" t="n">
@@ -12690,7 +12861,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12731,20 +12902,20 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>545361</v>
+        <v>687263</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -12804,7 +12975,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12845,20 +13016,20 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>694384</v>
+        <v>545361</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R108" t="n">
@@ -12918,7 +13089,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12959,20 +13130,20 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>624585</v>
+        <v>694384</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -13032,7 +13203,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13073,20 +13244,20 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>666176</v>
+        <v>624585</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R110" t="n">
@@ -13146,7 +13317,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13187,20 +13358,20 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>666139</v>
+        <v>666176</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -13260,7 +13431,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13301,20 +13472,20 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>672724</v>
+        <v>666139</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R112" t="n">
@@ -13374,7 +13545,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13415,20 +13586,20 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>694203</v>
+        <v>672724</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -13488,7 +13659,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13529,20 +13700,20 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>681351</v>
+        <v>694203</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R114" t="n">
@@ -13602,15 +13773,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>823842</v>
+        <v>823681</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13628,35 +13799,35 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>672640</v>
+        <v>681351</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -13716,7 +13887,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13757,20 +13928,20 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>681715</v>
+        <v>672640</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R116" t="n">
@@ -13830,7 +14001,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13871,20 +14042,20 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>689414</v>
+        <v>681715</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -13944,7 +14115,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -13985,20 +14156,20 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>669364</v>
+        <v>689414</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -14058,7 +14229,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14099,20 +14270,20 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>691594</v>
+        <v>669364</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -14172,7 +14343,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14213,20 +14384,20 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Leo Jiménez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>677870</v>
+        <v>691594</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R120" t="n">
@@ -14286,7 +14457,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14327,20 +14498,20 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Leo Jiménez</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>665923</v>
+        <v>677870</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -14400,7 +14571,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14441,20 +14612,20 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Rece Hinds</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>677956</v>
+        <v>665923</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R122" t="n">
@@ -14514,7 +14685,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14555,20 +14726,20 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>640459</v>
+        <v>677956</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -14628,77 +14799,68 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>823358</v>
+        <v>823842</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>3</v>
-      </c>
-      <c r="I124" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" t="n">
-        <v>2</v>
+          <t>Top</t>
+        </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>592885</v>
+        <v>640459</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
         <v>0</v>
@@ -14751,7 +14913,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14764,22 +14926,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
         <v>2</v>
@@ -14863,7 +15025,7 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -14874,7 +15036,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -14887,22 +15049,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>2</v>
@@ -14986,7 +15148,7 @@
         <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -14997,7 +15159,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15010,22 +15172,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>2</v>
@@ -15109,7 +15271,7 @@
         <v>0</v>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -15120,7 +15282,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15133,22 +15295,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
         <v>2</v>
@@ -15232,7 +15394,7 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -15243,7 +15405,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15256,22 +15418,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>2</v>
@@ -15355,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -15366,7 +15528,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15379,22 +15541,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>2</v>
@@ -15478,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="AG130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -15489,7 +15651,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15502,22 +15664,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>2</v>
@@ -15601,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="AG131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -15612,7 +15774,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15625,22 +15787,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>2</v>
@@ -15724,7 +15886,7 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -15735,7 +15897,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15849,7 +16011,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15963,7 +16125,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16077,7 +16239,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16191,7 +16353,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16305,7 +16467,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16419,7 +16581,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16533,7 +16695,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16647,7 +16809,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16761,7 +16923,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16875,7 +17037,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16989,7 +17151,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17103,7 +17265,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17217,7 +17379,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17331,7 +17493,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17445,7 +17607,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17559,7 +17721,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17673,7 +17835,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17787,7 +17949,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17901,7 +18063,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18015,7 +18177,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18129,7 +18291,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18243,7 +18405,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18357,7 +18519,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18471,7 +18633,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18585,7 +18747,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18699,7 +18861,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18813,7 +18975,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18927,7 +19089,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19041,7 +19203,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19155,7 +19317,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19269,7 +19431,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19383,7 +19545,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19497,7 +19659,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19611,7 +19773,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19725,7 +19887,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19839,7 +20001,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19852,22 +20014,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
         <v>2</v>
@@ -19962,7 +20124,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19975,22 +20137,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>2</v>
@@ -20085,7 +20247,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20098,22 +20260,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>2</v>
@@ -20208,7 +20370,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20221,22 +20383,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bottom 3 | 3 out</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>2</v>
@@ -20331,7 +20493,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20437,7 +20599,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20543,7 +20705,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20649,7 +20811,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20755,7 +20917,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20861,7 +21023,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20967,7 +21129,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21073,7 +21235,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21179,7 +21341,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:35 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21285,7 +21447,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21399,7 +21561,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21513,7 +21675,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21627,7 +21789,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21741,7 +21903,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21855,7 +22017,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21969,7 +22131,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22083,7 +22245,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22197,7 +22359,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22311,7 +22473,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22417,7 +22579,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22523,7 +22685,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22629,7 +22791,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22735,7 +22897,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22841,7 +23003,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22947,7 +23109,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23053,7 +23215,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23159,7 +23321,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23265,7 +23427,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23379,7 +23541,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23493,7 +23655,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23607,7 +23769,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23721,7 +23883,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23835,7 +23997,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -23949,7 +24111,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24063,7 +24225,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24177,7 +24339,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24291,7 +24453,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24405,7 +24567,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24519,7 +24681,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24633,7 +24795,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24747,7 +24909,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -24861,7 +25023,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -24975,7 +25137,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25089,7 +25251,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25203,7 +25365,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25317,7 +25479,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25431,7 +25593,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25545,7 +25707,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25659,7 +25821,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25773,7 +25935,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -25887,7 +26049,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26001,7 +26163,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26115,7 +26277,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26229,7 +26391,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:34 AM PT</t>
+          <t>2026-07-12 10:07:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26343,7 +26505,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26457,7 +26619,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26571,7 +26733,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26685,7 +26847,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26799,7 +26961,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26913,7 +27075,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27027,7 +27189,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27141,7 +27303,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27255,7 +27417,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:05:33 AM PT</t>
+          <t>2026-07-12 10:07:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -952,39 +952,39 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Esmerlyn Valdez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>699013</v>
+        <v>592885</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1030,10 +1030,10 @@
         <v>7</v>
       </c>
       <c r="AF4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1075,56 +1075,56 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Jackson Chourio</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>694192</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Marcell Ozuna</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>542303</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1198,39 +1198,39 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Esmerlyn Valdez</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>592885</v>
+        <v>699013</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1273,13 +1273,13 @@
         <v>0</v>
       </c>
       <c r="AE6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
         <v>5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1321,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1340,27 +1340,27 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>668804</v>
+        <v>542303</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1378,10 +1378,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>4</v>
@@ -1413,74 +1413,83 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>824574</v>
+        <v>823358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 4 | 0 out</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bryan Reynolds</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>668804</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Jacob Wilson</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>805779</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1507,16 +1516,16 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1527,7 +1536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1568,20 +1577,20 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>811965</v>
+        <v>805779</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1641,7 +1650,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1682,20 +1691,20 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>669127</v>
+        <v>811965</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1755,7 +1764,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1796,20 +1805,20 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>641680</v>
+        <v>669127</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1869,7 +1878,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1910,20 +1919,20 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Colby Thomas</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>687515</v>
+        <v>641680</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R12" t="n">
@@ -1983,7 +1992,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2024,20 +2033,20 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Joey Meneses</t>
+          <t>Colby Thomas</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>608841</v>
+        <v>687515</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -2097,7 +2106,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2138,20 +2147,20 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Joey Meneses</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>671732</v>
+        <v>608841</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -2211,7 +2220,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2252,20 +2261,20 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>703607</v>
+        <v>671732</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2325,7 +2334,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2366,20 +2375,20 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>675961</v>
+        <v>703607</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R16" t="n">
@@ -2439,15 +2448,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>823029</v>
+        <v>824574</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2470,30 +2479,30 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>686948</v>
+        <v>675961</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2553,7 +2562,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2594,20 +2603,20 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>645277</v>
+        <v>686948</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2667,7 +2676,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2708,20 +2717,20 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>621566</v>
+        <v>645277</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2781,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2822,20 +2831,20 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>671739</v>
+        <v>621566</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2895,7 +2904,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2936,20 +2945,20 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>643289</v>
+        <v>671739</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -3009,7 +3018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3050,20 +3059,20 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>642086</v>
+        <v>643289</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R22" t="n">
@@ -3123,7 +3132,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3164,20 +3173,20 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>663586</v>
+        <v>642086</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -3237,7 +3246,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3278,20 +3287,20 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>805347</v>
+        <v>663586</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -3351,7 +3360,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3392,20 +3401,20 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>676551</v>
+        <v>805347</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -3465,20 +3474,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>824814</v>
+        <v>823029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Top 1 | 0 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3489,46 +3498,37 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>683002</v>
+        <v>676551</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3638,20 +3638,20 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>621493</v>
+        <v>683002</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3761,20 +3761,20 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>687637</v>
+        <v>621493</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3884,20 +3884,20 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>624413</v>
+        <v>687637</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4007,20 +4007,20 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>694212</v>
+        <v>624413</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4130,20 +4130,20 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Blaze Alexander</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>677942</v>
+        <v>694212</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4253,20 +4253,20 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Blaze Alexander</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>681297</v>
+        <v>677942</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4376,20 +4376,20 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>665750</v>
+        <v>681297</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4499,20 +4499,20 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>702616</v>
+        <v>665750</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -4572,20 +4572,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>823602</v>
+        <v>824814</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4596,28 +4596,37 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>678011</v>
+        <v>702616</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4626,7 +4635,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -4686,7 +4695,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4727,20 +4736,20 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>678882</v>
+        <v>678011</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -4800,7 +4809,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4841,20 +4850,20 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>677800</v>
+        <v>678882</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -4914,7 +4923,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4955,20 +4964,20 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Romy Gonzalez</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>663853</v>
+        <v>677800</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -5028,7 +5037,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5069,20 +5078,20 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Romy Gonzalez</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>702332</v>
+        <v>663853</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -5142,7 +5151,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5183,20 +5192,20 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>655316</v>
+        <v>702332</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -5256,7 +5265,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5297,20 +5306,20 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>680776</v>
+        <v>655316</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -5370,7 +5379,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5411,20 +5420,20 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>681987</v>
+        <v>680776</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -5484,7 +5493,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5525,20 +5534,20 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>657136</v>
+        <v>681987</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -5598,11 +5607,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>824491</v>
+        <v>823602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5629,30 +5638,30 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>691718</v>
+        <v>657136</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -5712,7 +5721,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5753,20 +5762,20 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>673548</v>
+        <v>691718</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -5826,7 +5835,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5867,20 +5876,20 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>608324</v>
+        <v>673548</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -5940,7 +5949,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5981,20 +5990,20 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>608348</v>
+        <v>608324</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -6054,7 +6063,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6095,20 +6104,20 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>683737</v>
+        <v>608348</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -6168,7 +6177,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6209,20 +6218,20 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>663538</v>
+        <v>683737</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -6282,7 +6291,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6323,20 +6332,20 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>664023</v>
+        <v>663538</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -6396,7 +6405,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6437,20 +6446,20 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>621020</v>
+        <v>664023</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -6510,7 +6519,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6551,20 +6560,20 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Kevin Alcántara</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>682634</v>
+        <v>621020</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -6624,7 +6633,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6650,35 +6659,35 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Kevin Alcántara</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>682829</v>
+        <v>682634</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -6738,7 +6747,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6779,20 +6788,20 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>701398</v>
+        <v>682829</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R54" t="n">
@@ -6852,7 +6861,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6893,20 +6902,20 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>668715</v>
+        <v>701398</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -6966,7 +6975,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7007,20 +7016,20 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>668709</v>
+        <v>668715</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R56" t="n">
@@ -7080,7 +7089,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7121,20 +7130,20 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>553993</v>
+        <v>668709</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -7194,7 +7203,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7235,20 +7244,20 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>663886</v>
+        <v>553993</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R58" t="n">
@@ -7308,7 +7317,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7349,20 +7358,20 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>682622</v>
+        <v>663886</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -7422,7 +7431,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7463,20 +7472,20 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Edwin Arroyo</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>695490</v>
+        <v>682622</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R60" t="n">
@@ -7536,7 +7545,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7577,20 +7586,20 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Edwin Arroyo</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>663647</v>
+        <v>695490</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R61" t="n">
@@ -7650,11 +7659,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>823842</v>
+        <v>824491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7676,35 +7685,35 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>683953</v>
+        <v>663647</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -7764,7 +7773,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7805,20 +7814,20 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>677587</v>
+        <v>683953</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -7878,7 +7887,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7919,20 +7928,20 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>800050</v>
+        <v>677587</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -7992,7 +8001,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8033,20 +8042,20 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>700932</v>
+        <v>800050</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -8106,7 +8115,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8147,20 +8156,20 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R66" t="n">
@@ -8220,7 +8229,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8261,20 +8270,20 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>672356</v>
+        <v>696135</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8334,7 +8343,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8375,20 +8384,20 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>690984</v>
+        <v>672356</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R68" t="n">
@@ -8448,7 +8457,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8489,20 +8498,20 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>672275</v>
+        <v>690984</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -8562,7 +8571,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8603,20 +8612,20 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>680757</v>
+        <v>672275</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -8676,15 +8685,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>824574</v>
+        <v>823842</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8702,26 +8711,26 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>803011</v>
+        <v>680757</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -8730,7 +8739,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8790,7 +8799,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8831,20 +8840,20 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>808959</v>
+        <v>803011</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -8904,7 +8913,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8945,20 +8954,20 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>678246</v>
+        <v>808959</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -9018,7 +9027,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9059,20 +9068,20 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>695657</v>
+        <v>678246</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -9132,7 +9141,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9173,20 +9182,20 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>643217</v>
+        <v>695657</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -9246,7 +9255,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9287,20 +9296,20 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>691019</v>
+        <v>643217</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R76" t="n">
@@ -9360,7 +9369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9401,20 +9410,20 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>695731</v>
+        <v>691019</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9474,7 +9483,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9515,20 +9524,20 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>671976</v>
+        <v>695731</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R78" t="n">
@@ -9588,7 +9597,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9629,20 +9638,20 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>805367</v>
+        <v>671976</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -9702,15 +9711,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>824250</v>
+        <v>824574</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9733,30 +9742,30 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>805808</v>
+        <v>805367</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R80" t="n">
@@ -9816,7 +9825,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9857,20 +9866,20 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>693307</v>
+        <v>805808</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -9930,7 +9939,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9971,20 +9980,20 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>690993</v>
+        <v>693307</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R82" t="n">
@@ -10044,7 +10053,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10085,20 +10094,20 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>682985</v>
+        <v>690993</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -10158,7 +10167,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10199,20 +10208,20 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>679529</v>
+        <v>682985</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R84" t="n">
@@ -10272,7 +10281,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10313,20 +10322,20 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Kerry Carpenter</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>681481</v>
+        <v>679529</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -10386,7 +10395,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10427,20 +10436,20 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Kerry Carpenter</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>656716</v>
+        <v>681481</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R86" t="n">
@@ -10500,7 +10509,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10541,20 +10550,20 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>663837</v>
+        <v>656716</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -10614,7 +10623,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10655,20 +10664,20 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>681546</v>
+        <v>663837</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R88" t="n">
@@ -10728,15 +10737,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>822876</v>
+        <v>824250</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10754,35 +10763,35 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>665161</v>
+        <v>681546</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R89" t="n">
@@ -10842,7 +10851,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10883,20 +10892,20 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>670541</v>
+        <v>665161</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R90" t="n">
@@ -10956,7 +10965,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -10997,20 +11006,20 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>670623</v>
+        <v>670541</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -11070,7 +11079,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11111,20 +11120,20 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>572233</v>
+        <v>670623</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R92" t="n">
@@ -11184,7 +11193,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11225,20 +11234,20 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>514888</v>
+        <v>572233</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -11298,7 +11307,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11339,20 +11348,20 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>701358</v>
+        <v>514888</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R94" t="n">
@@ -11412,7 +11421,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11453,20 +11462,20 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>664774</v>
+        <v>701358</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -11526,7 +11535,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11567,20 +11576,20 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Brice Matthews</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>694728</v>
+        <v>664774</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R96" t="n">
@@ -11640,7 +11649,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11681,20 +11690,20 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Brice Matthews</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>543877</v>
+        <v>694728</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R97" t="n">
@@ -11754,20 +11763,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>824814</v>
+        <v>822876</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Top 1 | 0 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -11778,15 +11787,6 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Away</t>
@@ -11794,21 +11794,21 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>695600</v>
+        <v>543877</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R98" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11927,20 +11927,20 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>677951</v>
+        <v>695600</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12050,20 +12050,20 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>695506</v>
+        <v>677951</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R100" t="n">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12173,20 +12173,20 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>657041</v>
+        <v>695506</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R101" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12296,20 +12296,20 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>686469</v>
+        <v>657041</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R102" t="n">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12419,20 +12419,20 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>521692</v>
+        <v>686469</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12542,20 +12542,20 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>686681</v>
+        <v>521692</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12665,20 +12665,20 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Josh Rojas</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>668942</v>
+        <v>686681</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12788,20 +12788,20 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Rojas</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>686555</v>
+        <v>668942</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R106" t="n">
@@ -12861,20 +12861,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>823681</v>
+        <v>824814</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -12885,6 +12885,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>Away</t>
@@ -12892,30 +12901,30 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>687263</v>
+        <v>686555</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -12975,7 +12984,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13016,20 +13025,20 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>545361</v>
+        <v>687263</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R108" t="n">
@@ -13089,7 +13098,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13130,20 +13139,20 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>694384</v>
+        <v>545361</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -13203,7 +13212,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13244,20 +13253,20 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>624585</v>
+        <v>694384</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R110" t="n">
@@ -13317,7 +13326,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13358,20 +13367,20 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>666176</v>
+        <v>624585</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -13431,7 +13440,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13472,20 +13481,20 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>666139</v>
+        <v>666176</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R112" t="n">
@@ -13545,7 +13554,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13586,20 +13595,20 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>672724</v>
+        <v>666139</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -13659,7 +13668,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13700,20 +13709,20 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>694203</v>
+        <v>672724</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R114" t="n">
@@ -13773,7 +13782,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13814,20 +13823,20 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>681351</v>
+        <v>694203</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -13887,15 +13896,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>823842</v>
+        <v>823681</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -13913,35 +13922,35 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>672640</v>
+        <v>681351</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R116" t="n">
@@ -14001,7 +14010,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14042,20 +14051,20 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>681715</v>
+        <v>672640</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -14115,7 +14124,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14156,20 +14165,20 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>689414</v>
+        <v>681715</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -14229,7 +14238,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14270,20 +14279,20 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>669364</v>
+        <v>689414</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -14343,7 +14352,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14384,20 +14393,20 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>691594</v>
+        <v>669364</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R120" t="n">
@@ -14457,7 +14466,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14498,20 +14507,20 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Leo Jiménez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>677870</v>
+        <v>691594</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -14571,7 +14580,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14612,20 +14621,20 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Leo Jiménez</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>665923</v>
+        <v>677870</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R122" t="n">
@@ -14685,7 +14694,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14726,20 +14735,20 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Rece Hinds</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>677956</v>
+        <v>665923</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -14799,7 +14808,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14840,20 +14849,20 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>640459</v>
+        <v>677956</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R124" t="n">
@@ -14913,77 +14922,68 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>823358</v>
+        <v>823842</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Top 4 | 0 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>2</v>
-      </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>694192</v>
+        <v>640459</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
         <v>0</v>
@@ -15016,7 +15016,7 @@
         <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE125" s="4" t="n">
         <v>0</v>
@@ -15025,7 +15025,7 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -15145,10 +15145,10 @@
         <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15190,7 +15190,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15268,10 +15268,10 @@
         <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15313,7 +15313,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15391,10 +15391,10 @@
         <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15436,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15514,10 +15514,10 @@
         <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15559,7 +15559,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15637,10 +15637,10 @@
         <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15682,7 +15682,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15760,10 +15760,10 @@
         <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15805,7 +15805,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -15883,10 +15883,10 @@
         <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -17972,6 +17972,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -18063,7 +18072,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18076,7 +18085,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -18086,6 +18095,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -18177,7 +18195,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18190,7 +18208,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -18200,6 +18218,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -18291,7 +18318,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18304,7 +18331,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -18314,6 +18341,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -18405,7 +18441,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18418,7 +18454,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -18428,6 +18464,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -18519,7 +18564,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18532,7 +18577,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18542,6 +18587,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18633,7 +18687,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18646,7 +18700,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18656,6 +18710,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18747,7 +18810,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18760,7 +18823,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18770,6 +18833,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18861,7 +18933,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18874,7 +18946,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18884,6 +18956,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18975,7 +19056,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19089,7 +19170,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19203,7 +19284,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19317,7 +19398,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19431,7 +19512,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19545,7 +19626,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19659,7 +19740,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19773,7 +19854,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19887,7 +19968,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -20001,7 +20082,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20032,7 +20113,7 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -20124,7 +20205,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20155,7 +20236,7 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -20247,7 +20328,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20278,7 +20359,7 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -20370,7 +20451,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20401,7 +20482,7 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -20493,7 +20574,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20599,7 +20680,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20705,7 +20786,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20811,7 +20892,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20917,7 +20998,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -21023,7 +21104,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21129,7 +21210,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21235,7 +21316,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21341,7 +21422,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21447,7 +21528,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21561,7 +21642,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21675,7 +21756,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21789,7 +21870,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21903,7 +21984,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22017,7 +22098,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22131,7 +22212,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22245,7 +22326,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22359,7 +22440,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22473,7 +22554,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22579,7 +22660,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22685,7 +22766,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22791,7 +22872,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22897,7 +22978,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23003,7 +23084,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23109,7 +23190,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23215,7 +23296,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23321,7 +23402,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:35 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23427,7 +23508,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23541,7 +23622,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23655,7 +23736,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23769,7 +23850,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23883,7 +23964,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -23997,7 +24078,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24111,7 +24192,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24225,7 +24306,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24339,7 +24420,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24453,7 +24534,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24567,7 +24648,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24681,7 +24762,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24795,7 +24876,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24909,7 +24990,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25023,7 +25104,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25137,7 +25218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25251,7 +25332,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25365,7 +25446,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25479,7 +25560,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25593,7 +25674,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25707,7 +25788,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25821,7 +25902,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -25935,7 +26016,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26049,7 +26130,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26163,7 +26244,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26277,7 +26358,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26391,7 +26472,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:34 AM PT</t>
+          <t>2026-07-12 10:09:34 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26505,7 +26586,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26518,7 +26599,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -26528,6 +26609,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -26619,7 +26709,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26632,7 +26722,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -26642,6 +26732,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -26733,7 +26832,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26746,7 +26845,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -26756,6 +26855,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -26847,7 +26955,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -26860,7 +26968,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -26870,6 +26978,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -26961,7 +27078,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -26974,7 +27091,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -26984,6 +27101,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -27075,7 +27201,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27088,7 +27214,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -27098,6 +27224,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -27189,7 +27324,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27202,7 +27337,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -27212,6 +27347,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -27303,7 +27447,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27316,7 +27460,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -27326,6 +27470,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -27417,7 +27570,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:07:33 AM PT</t>
+          <t>2026-07-12 10:09:33 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27430,7 +27583,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -27440,6 +27593,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -694,7 +694,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -706,13 +706,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -940,7 +940,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -977,20 +977,20 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>592885</v>
+        <v>694192</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1018,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
         <v>2</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1100,20 +1100,20 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>694192</v>
+        <v>592885</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="4" t="n">
         <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>2</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
         <v>2</v>
@@ -1665,90 +1665,99 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>824574</v>
+        <v>823358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>9:15 AM PT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Gary Sánchez</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>596142</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Jacob Wilson</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>805779</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
@@ -1762,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="AE10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1779,7 +1788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1820,20 +1829,20 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>811965</v>
+        <v>805779</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1893,7 +1902,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1934,20 +1943,20 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>669127</v>
+        <v>811965</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R12" t="n">
@@ -2007,7 +2016,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2048,20 +2057,20 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>641680</v>
+        <v>669127</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -2121,7 +2130,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2162,20 +2171,20 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Colby Thomas</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>687515</v>
+        <v>641680</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -2235,7 +2244,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2276,20 +2285,20 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Joey Meneses</t>
+          <t>Colby Thomas</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>608841</v>
+        <v>687515</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2349,7 +2358,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2390,20 +2399,20 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Joey Meneses</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>671732</v>
+        <v>608841</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R16" t="n">
@@ -2463,7 +2472,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2504,20 +2513,20 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>703607</v>
+        <v>671732</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2577,7 +2586,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2618,20 +2627,20 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>675961</v>
+        <v>703607</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2691,15 +2700,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>823029</v>
+        <v>824574</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11:15 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2722,30 +2731,30 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>686948</v>
+        <v>675961</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2805,7 +2814,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2846,20 +2855,20 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>645277</v>
+        <v>686948</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2919,7 +2928,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2960,20 +2969,20 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>621566</v>
+        <v>645277</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -3033,7 +3042,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3074,20 +3083,20 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>671739</v>
+        <v>621566</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R22" t="n">
@@ -3147,7 +3156,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3188,20 +3197,20 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>643289</v>
+        <v>671739</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -3261,7 +3270,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3302,20 +3311,20 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>642086</v>
+        <v>643289</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -3375,7 +3384,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3416,20 +3425,20 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>663586</v>
+        <v>642086</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -3489,7 +3498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3530,20 +3539,20 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>805347</v>
+        <v>663586</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -3603,7 +3612,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3644,20 +3653,20 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>676551</v>
+        <v>805347</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -3717,20 +3726,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>824814</v>
+        <v>823029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:15 AM PT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Top 1 | 0 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3741,46 +3750,37 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>683002</v>
+        <v>676551</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3890,20 +3890,20 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>621493</v>
+        <v>683002</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4013,20 +4013,20 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>687637</v>
+        <v>621493</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4136,20 +4136,20 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>624413</v>
+        <v>687637</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4259,20 +4259,20 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>694212</v>
+        <v>624413</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4382,20 +4382,20 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Blaze Alexander</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>677942</v>
+        <v>694212</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4505,20 +4505,20 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Blaze Alexander</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>681297</v>
+        <v>677942</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4628,20 +4628,20 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>665750</v>
+        <v>681297</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4751,20 +4751,20 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>702616</v>
+        <v>665750</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -4824,20 +4824,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>823602</v>
+        <v>824814</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4848,28 +4848,37 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>678011</v>
+        <v>702616</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4878,7 +4887,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -4938,7 +4947,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4951,7 +4960,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4962,6 +4971,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Away</t>
@@ -4979,20 +4997,20 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>678882</v>
+        <v>678011</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -5052,7 +5070,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5065,7 +5083,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5076,6 +5094,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5093,20 +5120,20 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>677800</v>
+        <v>678882</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -5166,7 +5193,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5179,7 +5206,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5190,6 +5217,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5207,20 +5243,20 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Romy Gonzalez</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>663853</v>
+        <v>677800</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -5280,7 +5316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5293,7 +5329,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5304,6 +5340,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5321,20 +5366,20 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Romy Gonzalez</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>702332</v>
+        <v>663853</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -5394,7 +5439,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5407,7 +5452,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5418,6 +5463,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5435,20 +5489,20 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>655316</v>
+        <v>702332</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -5508,7 +5562,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5521,7 +5575,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5532,6 +5586,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5549,20 +5612,20 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>680776</v>
+        <v>655316</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -5622,7 +5685,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5635,7 +5698,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5646,6 +5709,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5663,20 +5735,20 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>681987</v>
+        <v>680776</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -5736,7 +5808,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5749,7 +5821,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5760,6 +5832,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5777,20 +5858,20 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>657136</v>
+        <v>681987</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -5850,11 +5931,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>824491</v>
+        <v>823602</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5863,7 +5944,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5874,6 +5955,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>Away</t>
@@ -5881,30 +5971,30 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>691718</v>
+        <v>657136</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -5964,7 +6054,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6005,20 +6095,20 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>673548</v>
+        <v>691718</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -6078,7 +6168,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6119,20 +6209,20 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>608324</v>
+        <v>673548</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -6192,7 +6282,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6233,20 +6323,20 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>608348</v>
+        <v>608324</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -6306,7 +6396,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6347,20 +6437,20 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>683737</v>
+        <v>608348</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -6420,7 +6510,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6461,20 +6551,20 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>663538</v>
+        <v>683737</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -6534,7 +6624,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6575,20 +6665,20 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>664023</v>
+        <v>663538</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -6648,7 +6738,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6689,20 +6779,20 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>621020</v>
+        <v>664023</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -6762,7 +6852,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6803,20 +6893,20 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Kevin Alcántara</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>682634</v>
+        <v>621020</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R54" t="n">
@@ -6876,7 +6966,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6902,35 +6992,35 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Kevin Alcántara</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>682829</v>
+        <v>682634</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -6990,7 +7080,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7031,20 +7121,20 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>701398</v>
+        <v>682829</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R56" t="n">
@@ -7104,7 +7194,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7145,20 +7235,20 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>668715</v>
+        <v>701398</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -7218,7 +7308,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7259,20 +7349,20 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>668709</v>
+        <v>668715</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R58" t="n">
@@ -7332,7 +7422,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7373,20 +7463,20 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>553993</v>
+        <v>668709</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -7446,7 +7536,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7487,20 +7577,20 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>663886</v>
+        <v>553993</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R60" t="n">
@@ -7560,7 +7650,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7601,20 +7691,20 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>682622</v>
+        <v>663886</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R61" t="n">
@@ -7674,7 +7764,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7715,20 +7805,20 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Edwin Arroyo</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>695490</v>
+        <v>682622</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -7788,7 +7878,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7829,20 +7919,20 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Edwin Arroyo</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>663647</v>
+        <v>695490</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -7902,11 +7992,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>823842</v>
+        <v>824491</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7928,35 +8018,35 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>683953</v>
+        <v>663647</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -8016,7 +8106,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8057,20 +8147,20 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>677587</v>
+        <v>683953</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -8130,7 +8220,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8171,20 +8261,20 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>800050</v>
+        <v>677587</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R66" t="n">
@@ -8244,7 +8334,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8285,20 +8375,20 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>700932</v>
+        <v>800050</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8358,7 +8448,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8399,20 +8489,20 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>696135</v>
+        <v>700932</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R68" t="n">
@@ -8472,7 +8562,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8513,20 +8603,20 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>672356</v>
+        <v>696135</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -8586,7 +8676,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8627,20 +8717,20 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>690984</v>
+        <v>672356</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -8700,7 +8790,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8741,20 +8831,20 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>672275</v>
+        <v>690984</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8814,7 +8904,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8855,20 +8945,20 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>680757</v>
+        <v>672275</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -8928,15 +9018,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>823199</v>
+        <v>823842</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1:05 PM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8959,30 +9049,30 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>664983</v>
+        <v>680757</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -9042,7 +9132,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9083,20 +9173,20 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>666160</v>
+        <v>664983</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -9156,7 +9246,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9197,20 +9287,20 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Hunter Goodman</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>696100</v>
+        <v>666160</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -9270,7 +9360,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9311,20 +9401,20 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Hunter Goodman</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>681198</v>
+        <v>696100</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R76" t="n">
@@ -9384,7 +9474,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9425,20 +9515,20 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>691720</v>
+        <v>681198</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9498,7 +9588,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9539,20 +9629,20 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>694249</v>
+        <v>691720</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R78" t="n">
@@ -9612,7 +9702,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9653,20 +9743,20 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Troy Johnston</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>687859</v>
+        <v>694249</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -9726,7 +9816,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9767,20 +9857,20 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Tyler Freeman</t>
+          <t>Troy Johnston</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>671289</v>
+        <v>687859</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R80" t="n">
@@ -9840,7 +9930,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9881,20 +9971,20 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Tyler Freeman</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>678662</v>
+        <v>671289</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -9954,15 +10044,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>824574</v>
+        <v>823199</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>1:05 PM PT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9980,35 +10070,35 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>803011</v>
+        <v>678662</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R82" t="n">
@@ -10068,7 +10158,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10109,20 +10199,20 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>808959</v>
+        <v>803011</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -10182,7 +10272,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10223,20 +10313,20 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>678246</v>
+        <v>808959</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R84" t="n">
@@ -10296,7 +10386,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10337,20 +10427,20 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>695657</v>
+        <v>678246</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -10410,7 +10500,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10451,20 +10541,20 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>643217</v>
+        <v>695657</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R86" t="n">
@@ -10524,7 +10614,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10565,20 +10655,20 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>691019</v>
+        <v>643217</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -10638,7 +10728,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10679,20 +10769,20 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>695731</v>
+        <v>691019</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R88" t="n">
@@ -10752,7 +10842,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10793,20 +10883,20 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>671976</v>
+        <v>695731</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R89" t="n">
@@ -10866,7 +10956,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10907,20 +10997,20 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>805367</v>
+        <v>671976</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R90" t="n">
@@ -10980,15 +11070,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>824250</v>
+        <v>824574</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -11011,30 +11101,30 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>805808</v>
+        <v>805367</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -11094,7 +11184,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11135,20 +11225,20 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>693307</v>
+        <v>805808</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R92" t="n">
@@ -11208,7 +11298,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11249,20 +11339,20 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>690993</v>
+        <v>693307</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -11322,7 +11412,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11363,20 +11453,20 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>682985</v>
+        <v>690993</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R94" t="n">
@@ -11436,7 +11526,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11477,20 +11567,20 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>679529</v>
+        <v>682985</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -11550,7 +11640,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11591,20 +11681,20 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Kerry Carpenter</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>681481</v>
+        <v>679529</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R96" t="n">
@@ -11664,7 +11754,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11705,20 +11795,20 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Kerry Carpenter</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>656716</v>
+        <v>681481</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R97" t="n">
@@ -11778,7 +11868,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11819,20 +11909,20 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>663837</v>
+        <v>656716</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R98" t="n">
@@ -11892,7 +11982,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11933,20 +12023,20 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>681546</v>
+        <v>663837</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -12006,15 +12096,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>822876</v>
+        <v>824250</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>11:35 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -12032,35 +12122,35 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>665161</v>
+        <v>681546</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R100" t="n">
@@ -12120,7 +12210,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12161,20 +12251,20 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>670541</v>
+        <v>665161</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R101" t="n">
@@ -12234,7 +12324,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12275,20 +12365,20 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>670623</v>
+        <v>670541</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R102" t="n">
@@ -12348,7 +12438,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12389,20 +12479,20 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>572233</v>
+        <v>670623</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -12462,7 +12552,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12503,20 +12593,20 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>514888</v>
+        <v>572233</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -12576,7 +12666,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12617,20 +12707,20 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>701358</v>
+        <v>514888</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -12690,7 +12780,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12731,20 +12821,20 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>664774</v>
+        <v>701358</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R106" t="n">
@@ -12804,7 +12894,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12845,20 +12935,20 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Brice Matthews</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>694728</v>
+        <v>664774</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -12918,7 +13008,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12959,20 +13049,20 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Brice Matthews</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>543877</v>
+        <v>694728</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R108" t="n">
@@ -13032,20 +13122,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>824814</v>
+        <v>822876</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10:35 AM PT</t>
+          <t>11:35 AM PT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Top 1 | 0 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -13056,15 +13146,6 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>Away</t>
@@ -13072,21 +13153,21 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>695600</v>
+        <v>543877</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -13095,7 +13176,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -13155,7 +13236,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13205,20 +13286,20 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>677951</v>
+        <v>695600</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R110" t="n">
@@ -13278,7 +13359,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13328,20 +13409,20 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Jac Caglianone</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>695506</v>
+        <v>677951</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -13401,7 +13482,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13451,20 +13532,20 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Jac Caglianone</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>657041</v>
+        <v>695506</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R112" t="n">
@@ -13524,7 +13605,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13574,20 +13655,20 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>686469</v>
+        <v>657041</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -13647,7 +13728,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13697,20 +13778,20 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>521692</v>
+        <v>686469</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R114" t="n">
@@ -13770,7 +13851,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13820,20 +13901,20 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>686681</v>
+        <v>521692</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -13893,7 +13974,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13943,20 +14024,20 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Josh Rojas</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>668942</v>
+        <v>686681</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R116" t="n">
@@ -14016,7 +14097,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14066,20 +14147,20 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Rojas</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>686555</v>
+        <v>668942</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -14139,20 +14220,20 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>823681</v>
+        <v>824814</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>11:10 AM PT</t>
+          <t>10:35 AM PT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -14163,6 +14244,15 @@
           <t>Top</t>
         </is>
       </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
           <t>Away</t>
@@ -14170,30 +14260,30 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>687263</v>
+        <v>686555</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -14253,7 +14343,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14294,20 +14384,20 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>545361</v>
+        <v>687263</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -14367,7 +14457,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14408,20 +14498,20 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>694384</v>
+        <v>545361</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R120" t="n">
@@ -14481,7 +14571,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14522,20 +14612,20 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Jorge Soler</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>624585</v>
+        <v>694384</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -14595,7 +14685,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14636,20 +14726,20 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jorge Soler</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>666176</v>
+        <v>624585</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R122" t="n">
@@ -14709,7 +14799,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14750,20 +14840,20 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>666139</v>
+        <v>666176</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -14823,7 +14913,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14864,20 +14954,20 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>672724</v>
+        <v>666139</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R124" t="n">
@@ -14937,7 +15027,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14978,20 +15068,20 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>694203</v>
+        <v>672724</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -15051,7 +15141,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15092,20 +15182,20 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>681351</v>
+        <v>694203</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R126" t="n">
@@ -15165,15 +15255,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>823925</v>
+        <v>823681</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1:10 PM PT</t>
+          <t>11:10 AM PT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -15181,37 +15271,45 @@
           <t>Pre-Game</t>
         </is>
       </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>660271</v>
+        <v>681351</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -15271,7 +15369,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15304,20 +15402,20 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>681624</v>
+        <v>660271</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R128" t="n">
@@ -15377,7 +15475,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15410,20 +15508,20 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>518692</v>
+        <v>681624</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R129" t="n">
@@ -15483,7 +15581,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15516,20 +15614,20 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>605141</v>
+        <v>518692</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R130" t="n">
@@ -15589,7 +15687,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15622,20 +15720,20 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>669242</v>
+        <v>605141</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R131" t="n">
@@ -15695,7 +15793,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15728,20 +15826,20 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>663656</v>
+        <v>669242</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R132" t="n">
@@ -15801,7 +15899,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15834,20 +15932,20 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>606192</v>
+        <v>663656</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R133" t="n">
@@ -15907,7 +16005,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -15940,20 +16038,20 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>571970</v>
+        <v>606192</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R134" t="n">
@@ -16013,7 +16111,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16046,20 +16144,20 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Eliezer Alfonzo</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>672613</v>
+        <v>571970</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -16119,15 +16217,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>823842</v>
+        <v>823925</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>10:40 AM PT</t>
+          <t>1:10 PM PT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -16135,14 +16233,6 @@
           <t>Pre-Game</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>Home</t>
@@ -16150,30 +16240,30 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>672640</v>
+        <v>672613</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R136" t="n">
@@ -16233,7 +16323,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16274,20 +16364,20 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>681715</v>
+        <v>672640</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R137" t="n">
@@ -16347,7 +16437,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16388,20 +16478,20 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>689414</v>
+        <v>681715</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R138" t="n">
@@ -16461,7 +16551,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16502,20 +16592,20 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>669364</v>
+        <v>689414</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -16575,7 +16665,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16616,20 +16706,20 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>691594</v>
+        <v>669364</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R140" t="n">
@@ -16689,7 +16779,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16730,20 +16820,20 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Leo Jiménez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>677870</v>
+        <v>691594</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -16803,7 +16893,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16844,20 +16934,20 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Leo Jiménez</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>665923</v>
+        <v>677870</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R142" t="n">
@@ -16917,7 +17007,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -16958,20 +17048,20 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Rece Hinds</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>677956</v>
+        <v>665923</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -17031,7 +17121,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17072,20 +17162,20 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>640459</v>
+        <v>677956</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R144" t="n">
@@ -17145,77 +17235,68 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>823358</v>
+        <v>823842</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>9:15 AM PT</t>
+          <t>10:40 AM PT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="H145" t="n">
-        <v>1</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n">
-        <v>1</v>
-      </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>668930</v>
+        <v>640459</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
         <v>0</v>
@@ -17254,10 +17335,10 @@
         <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -17268,7 +17349,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17281,7 +17362,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -17293,13 +17374,13 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17318,27 +17399,27 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>596142</v>
+        <v>668930</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T146" t="n">
         <v>0</v>
@@ -17377,7 +17458,7 @@
         <v>0</v>
       </c>
       <c r="AF146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG146" t="n">
         <v>2</v>
@@ -17391,7 +17472,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17404,7 +17485,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -17416,13 +17497,13 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -17500,7 +17581,7 @@
         <v>0</v>
       </c>
       <c r="AF147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG147" t="n">
         <v>2</v>
@@ -17514,7 +17595,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17527,7 +17608,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -17539,13 +17620,13 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -17623,7 +17704,7 @@
         <v>0</v>
       </c>
       <c r="AF148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG148" t="n">
         <v>2</v>
@@ -17637,7 +17718,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17650,7 +17731,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -17662,13 +17743,13 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -17746,7 +17827,7 @@
         <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG149" t="n">
         <v>2</v>
@@ -17760,7 +17841,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17773,7 +17854,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -17785,13 +17866,13 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -17869,7 +17950,7 @@
         <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG150" t="n">
         <v>2</v>
@@ -17883,7 +17964,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17997,7 +18078,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18111,7 +18192,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18225,7 +18306,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18339,7 +18420,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18453,7 +18534,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18567,7 +18648,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18681,7 +18762,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18795,7 +18876,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18909,7 +18990,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18922,7 +19003,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -18932,6 +19013,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -19023,7 +19113,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19036,7 +19126,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -19046,6 +19136,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -19137,7 +19236,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19150,7 +19249,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -19160,6 +19259,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -19251,7 +19359,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19264,7 +19372,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -19274,6 +19382,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -19365,7 +19482,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19378,7 +19495,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -19388,6 +19505,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -19479,7 +19605,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19492,7 +19618,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -19502,6 +19628,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -19593,7 +19728,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19606,7 +19741,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -19616,6 +19751,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -19707,7 +19851,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19720,7 +19864,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -19730,6 +19874,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -19821,7 +19974,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19834,7 +19987,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -19844,6 +19997,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -19935,7 +20097,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20058,7 +20220,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20181,7 +20343,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20304,7 +20466,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20427,7 +20589,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20550,7 +20712,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20673,7 +20835,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20796,7 +20958,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20919,7 +21081,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -21042,7 +21204,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21156,7 +21318,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21270,7 +21432,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21384,7 +21546,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21498,7 +21660,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21612,7 +21774,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21726,7 +21888,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21840,7 +22002,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21954,7 +22116,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22068,7 +22230,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22081,7 +22243,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -22093,13 +22255,13 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -22191,7 +22353,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22204,7 +22366,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -22216,13 +22378,13 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -22314,7 +22476,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22327,7 +22489,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -22339,13 +22501,13 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -22437,7 +22599,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22450,7 +22612,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Top 4 | 1 out</t>
+          <t>Top 4 | 2 out</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -22462,13 +22624,13 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -22560,7 +22722,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22666,7 +22828,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22772,7 +22934,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22878,7 +23040,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22984,7 +23146,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23090,7 +23252,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23196,7 +23358,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23302,7 +23464,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23408,7 +23570,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23514,7 +23676,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23628,7 +23790,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23742,7 +23904,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23856,7 +24018,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -23970,7 +24132,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24084,7 +24246,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24198,7 +24360,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24312,7 +24474,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24426,7 +24588,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24540,7 +24702,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24654,7 +24816,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24768,7 +24930,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24882,7 +25044,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -24996,7 +25158,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25110,7 +25272,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25224,7 +25386,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25338,7 +25500,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25452,7 +25614,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:08 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25566,7 +25728,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25680,7 +25842,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25794,7 +25956,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25908,7 +26070,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26022,7 +26184,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26136,7 +26298,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26250,7 +26412,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26364,7 +26526,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26478,7 +26640,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26592,7 +26754,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26706,7 +26868,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26820,7 +26982,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26934,7 +27096,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27048,7 +27210,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27162,7 +27324,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27276,7 +27438,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27390,7 +27552,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27504,7 +27666,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27618,7 +27780,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27732,7 +27894,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27846,7 +28008,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -27960,7 +28122,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28074,7 +28236,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28188,7 +28350,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28302,7 +28464,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28416,7 +28578,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28530,7 +28692,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:08 AM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28644,7 +28806,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28767,7 +28929,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -28890,7 +29052,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29013,7 +29175,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29136,7 +29298,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29259,7 +29421,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29382,7 +29544,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29505,7 +29667,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29628,7 +29790,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-12 10:13:07 AM PT</t>
+          <t>2026-07-12 10:15:07 AM PT</t>
         </is>
       </c>
       <c r="C253" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -475,7 +475,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -694,7 +694,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -702,11 +702,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -940,7 +940,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -948,11 +948,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1317,11 +1317,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1440,11 +1440,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8129,6 +8129,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8220,7 +8229,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8233,7 +8242,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8243,6 +8252,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8334,7 +8352,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8347,7 +8365,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8357,6 +8375,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8448,7 +8475,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8461,7 +8488,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -8471,6 +8498,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -8562,7 +8598,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8575,7 +8611,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -8585,6 +8621,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -8676,7 +8721,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8689,7 +8734,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -8699,6 +8744,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -8790,7 +8844,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8803,7 +8857,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8813,6 +8867,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8904,7 +8967,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8917,7 +8980,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8927,6 +8990,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9018,7 +9090,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9031,7 +9103,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -9041,6 +9113,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9132,7 +9213,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9246,7 +9327,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9360,7 +9441,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9474,7 +9555,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9588,7 +9669,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9702,7 +9783,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9816,7 +9897,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9930,7 +10011,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -10044,7 +10125,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10158,7 +10239,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10272,7 +10353,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10386,7 +10467,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10500,7 +10581,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10614,7 +10695,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10728,7 +10809,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10842,7 +10923,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10956,7 +11037,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -11070,7 +11151,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11184,7 +11265,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11298,7 +11379,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11412,7 +11493,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11526,7 +11607,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11640,7 +11721,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11754,7 +11835,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11868,7 +11949,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11982,7 +12063,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -12096,7 +12177,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12210,7 +12291,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12324,7 +12405,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12438,7 +12519,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12552,7 +12633,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12666,7 +12747,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12780,7 +12861,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12894,7 +12975,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -13008,7 +13089,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13122,7 +13203,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13236,7 +13317,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13359,7 +13440,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13482,7 +13563,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13605,7 +13686,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13728,7 +13809,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13851,7 +13932,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13974,7 +14055,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -14097,7 +14178,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14220,7 +14301,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14343,7 +14424,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14457,7 +14538,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14571,7 +14652,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14685,7 +14766,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14799,7 +14880,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14913,7 +14994,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -15027,7 +15108,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15141,7 +15222,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15255,7 +15336,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15369,7 +15450,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15475,7 +15556,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15581,7 +15662,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15687,7 +15768,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15793,7 +15874,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15899,7 +15980,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -16005,7 +16086,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16111,7 +16192,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16217,7 +16298,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16323,7 +16404,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16336,7 +16417,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -16346,6 +16427,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -16437,7 +16527,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16450,7 +16540,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -16460,6 +16550,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -16551,7 +16650,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16564,7 +16663,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -16574,6 +16673,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -16665,7 +16773,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16678,7 +16786,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -16688,6 +16796,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -16779,7 +16896,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16792,7 +16909,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -16802,6 +16919,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -16893,7 +17019,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16906,7 +17032,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -16916,6 +17042,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -17007,7 +17142,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17020,7 +17155,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -17030,6 +17165,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -17121,7 +17265,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17134,7 +17278,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -17144,6 +17288,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -17235,7 +17388,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17248,7 +17401,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -17258,6 +17411,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -17349,7 +17511,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17362,7 +17524,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -17370,11 +17532,11 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -17472,7 +17634,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17485,7 +17647,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -17493,11 +17655,11 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -17539,10 +17701,10 @@
         </is>
       </c>
       <c r="R147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T147" t="n">
         <v>0</v>
@@ -17595,7 +17757,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17608,7 +17770,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -17616,11 +17778,11 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
@@ -17718,7 +17880,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17731,7 +17893,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -17739,11 +17901,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -17841,7 +18003,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17854,7 +18016,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -17862,11 +18024,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -17964,7 +18126,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -18078,7 +18240,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18192,7 +18354,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18306,7 +18468,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18420,7 +18582,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18534,7 +18696,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18648,7 +18810,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18762,7 +18924,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18876,7 +19038,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18990,7 +19152,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19113,7 +19275,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19236,7 +19398,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19359,7 +19521,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19482,7 +19644,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19605,7 +19767,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19728,7 +19890,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19851,7 +20013,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19974,7 +20136,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -20097,7 +20259,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20220,7 +20382,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20343,7 +20505,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20466,7 +20628,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20589,7 +20751,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20712,7 +20874,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20835,7 +20997,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20958,7 +21120,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -21081,7 +21243,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -21204,7 +21366,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21318,7 +21480,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21432,7 +21594,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21546,7 +21708,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21660,7 +21822,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21774,7 +21936,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21888,7 +22050,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -22002,7 +22164,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -22116,7 +22278,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22230,7 +22392,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22243,7 +22405,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -22251,11 +22413,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
@@ -22353,7 +22515,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22366,7 +22528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -22374,11 +22536,11 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
@@ -22476,7 +22638,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22489,7 +22651,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -22497,11 +22659,11 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -22599,7 +22761,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22612,7 +22774,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Top 4 | 2 out</t>
+          <t>Bottom 4 | 0 out</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -22620,11 +22782,11 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -22722,7 +22884,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22828,7 +22990,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22934,7 +23096,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -23040,7 +23202,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -23146,7 +23308,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23252,7 +23414,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23358,7 +23520,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23464,7 +23626,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23570,7 +23732,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:08 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23676,7 +23838,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23790,7 +23952,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23904,7 +24066,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -24018,7 +24180,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -24132,7 +24294,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24246,7 +24408,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24360,7 +24522,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24474,7 +24636,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24588,7 +24750,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24702,7 +24864,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24816,7 +24978,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24930,7 +25092,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -25044,7 +25206,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25158,7 +25320,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25272,7 +25434,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25386,7 +25548,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25500,7 +25662,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25614,7 +25776,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25728,7 +25890,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25842,7 +26004,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25956,7 +26118,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -26070,7 +26232,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26184,7 +26346,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26298,7 +26460,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26412,7 +26574,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26526,7 +26688,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26640,7 +26802,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26754,7 +26916,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26868,7 +27030,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26982,7 +27144,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -27096,7 +27258,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27210,7 +27372,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27324,7 +27486,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27438,7 +27600,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27552,7 +27714,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27666,7 +27828,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27780,7 +27942,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27894,7 +28056,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -28008,7 +28170,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -28122,7 +28284,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28236,7 +28398,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28350,7 +28512,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28464,7 +28626,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28578,7 +28740,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28692,7 +28854,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:08 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28806,7 +28968,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28929,7 +29091,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -29052,7 +29214,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29175,7 +29337,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29298,7 +29460,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29421,7 +29583,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29544,7 +29706,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29667,7 +29829,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29790,7 +29952,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-12 10:15:07 AM PT</t>
+          <t>2026-07-12 10:17:07 AM PT</t>
         </is>
       </c>
       <c r="C253" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -731,33 +731,33 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>680779</v>
+        <v>542303</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
         <v>2</v>
@@ -787,13 +787,13 @@
         <v>0</v>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -804,7 +804,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -854,24 +854,24 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>656811</v>
+        <v>680779</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -882,26 +882,26 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="5" t="n">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" s="6" t="n">
-        <v>1</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -910,13 +910,13 @@
         <v>0</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -927,7 +927,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -958,46 +958,46 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>694192</v>
+        <v>656811</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -1023,23 +1023,23 @@
       <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
+      <c r="AB4" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1100,20 +1100,20 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>592885</v>
+        <v>694192</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1141,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1153,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF5" t="n">
         <v>2</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1204,39 +1204,39 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Esmerlyn Valdez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>699013</v>
+        <v>592885</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1282,10 +1282,10 @@
         <v>7</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1346,36 +1346,36 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Esmerlyn Valdez</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>542303</v>
+        <v>699013</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1405,10 +1405,10 @@
         <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -11288,6 +11288,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -11379,7 +11388,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11392,7 +11401,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11402,6 +11411,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -11493,7 +11511,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11506,7 +11524,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -11516,6 +11534,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -11607,7 +11634,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11620,7 +11647,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -11630,6 +11657,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -11721,7 +11757,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11734,7 +11770,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -11744,6 +11780,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -11835,7 +11880,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11848,7 +11893,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -11858,6 +11903,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -11949,7 +12003,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11962,7 +12016,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -11972,6 +12026,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -12063,7 +12126,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -12076,7 +12139,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -12086,6 +12149,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12177,7 +12249,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12190,7 +12262,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -12200,6 +12272,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -12291,7 +12372,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12405,7 +12486,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12519,7 +12600,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12633,7 +12714,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12747,7 +12828,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12861,7 +12942,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12975,7 +13056,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -13089,7 +13170,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13203,7 +13284,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13317,7 +13398,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13440,7 +13521,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13563,7 +13644,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13686,7 +13767,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13809,7 +13890,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13932,7 +14013,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -14055,7 +14136,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -14178,7 +14259,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14301,7 +14382,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14424,7 +14505,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14538,7 +14619,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14652,7 +14733,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14766,7 +14847,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14880,7 +14961,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14994,7 +15075,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -15108,7 +15189,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15222,7 +15303,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15336,7 +15417,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15450,7 +15531,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15556,7 +15637,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15662,7 +15743,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15768,7 +15849,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15874,7 +15955,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15980,7 +16061,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -16086,7 +16167,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16192,7 +16273,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16298,7 +16379,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16404,7 +16485,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16527,7 +16608,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16650,7 +16731,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16773,7 +16854,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16896,7 +16977,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -17019,7 +17100,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -17142,7 +17223,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17265,7 +17346,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17388,7 +17469,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17511,7 +17592,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17542,7 +17623,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17634,7 +17715,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17665,7 +17746,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -17757,7 +17838,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17788,7 +17869,7 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -17880,7 +17961,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17911,7 +17992,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -18003,7 +18084,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -18034,7 +18115,7 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -18126,7 +18207,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -18240,7 +18321,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18354,7 +18435,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18468,7 +18549,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18582,7 +18663,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18696,7 +18777,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18810,7 +18891,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18924,7 +19005,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -19038,7 +19119,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -19152,7 +19233,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19275,7 +19356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19398,7 +19479,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19521,7 +19602,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19644,7 +19725,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19767,7 +19848,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19890,7 +19971,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -20013,7 +20094,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -20136,7 +20217,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -20259,7 +20340,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20382,7 +20463,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20505,7 +20586,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20628,7 +20709,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20751,7 +20832,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20874,7 +20955,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20997,7 +21078,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -21120,7 +21201,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -21243,7 +21324,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -21366,7 +21447,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21379,7 +21460,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -21389,6 +21470,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -21480,7 +21570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21493,7 +21583,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -21503,6 +21593,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -21594,7 +21693,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21607,7 +21706,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -21617,6 +21716,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -21708,7 +21816,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21721,7 +21829,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -21731,6 +21839,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -21822,7 +21939,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21835,7 +21952,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -21845,6 +21962,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -21936,7 +22062,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21949,7 +22075,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -21959,6 +22085,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -22050,7 +22185,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -22063,7 +22198,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -22073,6 +22208,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -22164,7 +22308,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -22177,7 +22321,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -22187,6 +22331,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -22278,7 +22431,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22291,7 +22444,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Top 1 | 0 out</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -22301,6 +22454,15 @@
         <is>
           <t>Top</t>
         </is>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -22392,7 +22554,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22423,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -22501,10 +22663,10 @@
         <v>0</v>
       </c>
       <c r="AF187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
@@ -22515,7 +22677,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22546,7 +22708,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -22624,10 +22786,10 @@
         <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189">
@@ -22638,7 +22800,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22669,7 +22831,7 @@
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -22747,10 +22909,10 @@
         <v>0</v>
       </c>
       <c r="AF189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
@@ -22761,7 +22923,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22792,7 +22954,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -22870,10 +23032,10 @@
         <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191">
@@ -22884,7 +23046,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22990,7 +23152,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -23096,7 +23258,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -23202,7 +23364,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -23308,7 +23470,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23414,7 +23576,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23520,7 +23682,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23626,7 +23788,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23732,7 +23894,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:08 AM PT</t>
+          <t>2026-07-12 10:19:08 AM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23838,7 +24000,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23952,7 +24114,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -24066,7 +24228,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -24180,7 +24342,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -24294,7 +24456,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24408,7 +24570,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24522,7 +24684,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24636,7 +24798,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24750,7 +24912,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24864,7 +25026,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24978,7 +25140,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -25092,7 +25254,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -25206,7 +25368,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25320,7 +25482,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25434,7 +25596,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25548,7 +25710,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25662,7 +25824,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25776,7 +25938,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25890,7 +26052,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -26004,7 +26166,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -26118,7 +26280,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -26232,7 +26394,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26346,7 +26508,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26460,7 +26622,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26574,7 +26736,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26688,7 +26850,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26802,7 +26964,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26916,7 +27078,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -27030,7 +27192,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -27144,7 +27306,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -27258,7 +27420,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27372,7 +27534,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27486,7 +27648,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27600,7 +27762,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27714,7 +27876,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27828,7 +27990,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27942,7 +28104,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -28056,7 +28218,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -28170,7 +28332,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -28284,7 +28446,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28398,7 +28560,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28512,7 +28674,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28626,7 +28788,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28740,7 +28902,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28854,7 +29016,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28968,7 +29130,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -29091,7 +29253,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -29214,7 +29376,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29337,7 +29499,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29460,7 +29622,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29583,7 +29745,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29706,7 +29868,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29829,7 +29991,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29952,7 +30114,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-12 10:17:07 AM PT</t>
+          <t>2026-07-12 10:19:07 AM PT</t>
         </is>
       </c>
       <c r="C253" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5533,13 +5533,13 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6343,10 +6343,10 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8422,10 +8422,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -10531,10 +10531,10 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10615,10 +10615,10 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11308,10 +11308,10 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -12340,13 +12340,13 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12466,10 +12466,10 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12589,10 +12589,10 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -13051,13 +13051,13 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13519,10 +13519,10 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -13984,10 +13984,10 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -17410,13 +17410,13 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17650,10 +17650,10 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18001,10 +18001,10 @@
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18466,10 +18466,10 @@
         <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -18814,13 +18814,13 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -18937,13 +18937,13 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19177,10 +19177,10 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19300,10 +19300,10 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20563,10 +20563,10 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21484,10 +21484,10 @@
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -21946,13 +21946,13 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I186" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -22069,13 +22069,13 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22309,10 +22309,10 @@
         <v>1</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23458,10 +23458,10 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23581,10 +23581,10 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23904,7 +23904,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24616,10 +24616,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24739,10 +24739,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25290,7 +25290,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25660,10 +25660,10 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26224,7 +26224,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -26236,13 +26236,13 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26448,7 +26448,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26476,10 +26476,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26599,10 +26599,10 @@
         <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26722,10 +26722,10 @@
         <v>1</v>
       </c>
       <c r="I227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26845,10 +26845,10 @@
         <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -26884,10 +26884,10 @@
         </is>
       </c>
       <c r="R228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T228" t="n">
         <v>0</v>
@@ -26940,7 +26940,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -27054,7 +27054,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27282,7 +27282,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27510,7 +27510,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28194,7 +28194,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28336,10 +28336,10 @@
         <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28459,10 +28459,10 @@
         <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28582,10 +28582,10 @@
         <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28705,10 +28705,10 @@
         <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29598,7 +29598,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29826,7 +29826,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -30054,7 +30054,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30168,7 +30168,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30282,7 +30282,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30624,7 +30624,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30652,10 +30652,10 @@
         <v>1</v>
       </c>
       <c r="I261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30775,10 +30775,10 @@
         <v>1</v>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30898,10 +30898,10 @@
         <v>1</v>
       </c>
       <c r="I263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -31021,10 +31021,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -31230,7 +31230,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -31458,7 +31458,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -31572,7 +31572,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -31800,7 +31800,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -32028,7 +32028,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -32142,7 +32142,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -32256,7 +32256,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -32370,7 +32370,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -32598,7 +32598,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -33168,7 +33168,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -33282,7 +33282,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -33396,7 +33396,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -33624,7 +33624,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -33738,7 +33738,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -33852,7 +33852,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -33966,7 +33966,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -34080,7 +34080,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:15 PM PT</t>
+          <t>2026-07-12 03:19:30 PM PT</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -34321,7 +34321,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -34333,13 +34333,13 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I293" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J293" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -34456,13 +34456,13 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -34567,7 +34567,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -34579,13 +34579,13 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I296" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -34914,7 +34914,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -34942,10 +34942,10 @@
         <v>0</v>
       </c>
       <c r="I298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -35151,7 +35151,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -35607,7 +35607,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -35835,7 +35835,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -35949,7 +35949,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:17 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -36304,7 +36304,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -36316,13 +36316,13 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J310" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:18 PM PT</t>
+          <t>2026-07-12 03:19:32 PM PT</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -36427,7 +36427,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Top 8 | 0 out</t>
+          <t>Top 8 | 1 out</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -36439,13 +36439,13 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I311" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -36765,7 +36765,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -36879,7 +36879,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -36993,7 +36993,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-12 03:18:16 PM PT</t>
+          <t>2026-07-12 03:19:31 PM PT</t>
         </is>
       </c>
       <c r="C316" t="n">

--- a/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
+++ b/live_mlb_hitter_fantasy_scores_2026_07_12.xlsx
@@ -487,7 +487,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1405,7 +1405,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3468,17 +3468,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5529,17 +5529,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7150,7 +7150,7 @@
         <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -8301,17 +8301,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -10494,17 +10494,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10731,17 +10731,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -10854,17 +10854,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -11547,17 +11547,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -12582,17 +12582,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12712,7 +12712,7 @@
         <v>2</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>2</v>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12835,7 +12835,7 @@
         <v>2</v>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>2</v>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -13293,17 +13293,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T111" t="n">
         <v>1</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -13765,7 +13765,7 @@
         <v>2</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>2</v>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -14230,7 +14230,7 @@
         <v>2</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>2</v>
@@ -14325,7 +14325,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -17652,17 +17652,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17896,7 +17896,7 @@
         <v>2</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>2</v>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -18105,7 +18105,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -18240,17 +18240,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="R154" t="n">
+        <v>4</v>
+      </c>
+      <c r="S154" t="n">
         <v>3</v>
-      </c>
-      <c r="S154" t="n">
-        <v>2</v>
       </c>
       <c r="T154" t="n">
         <v>0</v>
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -18705,17 +18705,17 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -19056,17 +19056,17 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -19179,17 +19179,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19423,7 +19423,7 @@
         <v>2</v>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>2</v>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19546,7 +19546,7 @@
         <v>2</v>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>2</v>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20809,7 +20809,7 @@
         <v>2</v>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
         <v>2</v>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21730,7 +21730,7 @@
         <v>2</v>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>2</v>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -22053,7 +22053,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -22188,17 +22188,17 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23458,7 +23458,7 @@
         <v>2</v>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
         <v>2</v>
@@ -23553,7 +23553,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23581,7 +23581,7 @@
         <v>2</v>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>2</v>
@@ -23676,7 +23676,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -23904,7 +23904,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -24609,17 +24609,17 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -24732,17 +24732,17 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -25290,7 +25290,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -25660,7 +25660,7 @@
         <v>2</v>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
         <v>2</v>
@@ -25755,7 +25755,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -26224,7 +26224,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -26232,17 +26232,17 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Top 8 | 2 out</t>
+          <t>Bottom 8 | 0 out</t>
         </is>
       </c>
       <c r="F224" t="n">
@@ -26355,17 +26355,17 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -26584,7 +26584,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -26592,17 +26592,17 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -26715,17 +26715,17 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -26830,7 +26830,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -26838,17 +26838,17 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -26961,17 +26961,17 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -27177,7 +27177,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -27405,7 +27405,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -27747,7 +27747,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -28431,7 +28431,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -28459,7 +28459,7 @@
         <v>2</v>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J242" t="n">
         <v>2</v>
@@ -28554,7 +28554,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -28582,7 +28582,7 @@
         <v>2</v>
       </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J243" t="n">
         <v>2</v>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -28705,7 +28705,7 @@
         <v>2</v>
       </c>
       <c r="I244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J244" t="n">
         <v>2</v>
@@ -28800,7 +28800,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -28828,7 +28828,7 @@
         <v>2</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J245" t="n">
         <v>2</v>
@@ -28923,7 +28923,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -29265,7 +29265,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -29379,7 +29379,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -29721,7 +29721,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:30 PM PT</t>
+          <t>2026-07-12 03:25:30 PM PT</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -30291,7 +30291,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -30519,7 +30519,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:31 PM PT</t>
+          <t>2026-07-12 03:25:31 PM PT</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -30760,7 +30760,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -30768,17 +30768,17 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -30883,7 +30883,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Top 7 | 2 out</t>
+          <t>Bottom 7 | 0 out</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -30891,17 +30891,17 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-07-12 03:23:32 PM PT</t>
+          <t>2026-07-12 03:25:32 PM PT</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -31006,7 +31006,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Top 7 | 2 